--- a/input/images/tables/valueset-ref-all-list.xlsx
+++ b/input/images/tables/valueset-ref-all-list.xlsx
@@ -448,7 +448,7 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Descriptino</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -702,11 +702,7 @@
           <t>Care Team Member Function</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Created to group the old value set from HL7 code system with the new value set using SNOMEDCT and containing the extended set of care team member roles.</t>
-        </is>
-      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>StructureDefinition/us-core-careteam,StructureDefinition/us-core-practitionerrole</t>
@@ -872,7 +868,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>As noted in https://jira.hl7.org/browse/FHIR-32953, Drug class value set changed 2021-06-21 to align with C-CDA member value set 2.16.840.1.113762.1.4.1114.14</t>
+          <t>This set was initially developed in 2018. Annual updates to the value set definitions have retained inactivated codes and incorporated the suggested VSAC remaps. THERE WERE SOME MINOR CHANGES TO THE REFUTATIONS AND THE SCT CLASS SET IN 2021, BUT THERE HAVE BEEN NO SIGNIFICANT UPDATES TO REFLECT NEW DRUG CLASSES, NEW DRUG SUBSTANCES, NEW DIETARY SUBSTANCES, OR NEW ENVIRONMENTAL SUBSTANCES THAT MAY HAVE EMERGED SINCE 2018.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1050,7 +1046,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>20241214</v>
+        <v>20250702</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1126,7 +1122,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>20241008</v>
+        <v>20250610</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1286,7 +1282,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>20241105</v>
+        <v>20250529</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1310,7 +1306,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>This Specimen Condition SCT value set is an enumerated list created by the HL7 Orders and Observation WG’s lab subgroup to complement, without overlapping, the HL7 Specimen Condition value set (http://terminology.hl7.org/ValueSet/v2-0493). It is designed for use with the FHIR R4 Specimen Resource (https://hl7.org/fhir/R4/specimen.html), which has an extensible binding to the HL7 Specimen Condition value set. It can be used elsewhere and will be used in C-CDA. CAVEAT: 20 Additional codes will be added to this set (keeping the same scope) after the next publication of SCT in March 2025</t>
+          <t>This Specimen Condition SCT value set is an enumerated list created by the HL7 Orders and Observation WG’s lab subgroup to complement, without overlapping, the HL7 Specimen Condition value set (http://terminology.hl7.org/ValueSet/v2-0493). It is designed for use with the FHIR R4 Specimen Resource (https://hl7.org/fhir/R4/specimen.html), which has an extensible binding to the HL7 Specimen Condition value set. It can be used elsewhere and will be used in C-CDA.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1356,7 +1352,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>This value set is based on the US Core Detailed Race value set (http://hl7.org/fhir/us/core/ValueSet/detailed-race) but assigned a new OID due to its slightly different scope. It includes the CDCREC code 2131-1 (Other Race) in place of the HL7 nullFlavor code "OTH" (Other)</t>
+          <t>This value set is based on the US Core Detailed Race value set defined in US Core version 7.0 and earlier (https://hl7.org/fhir/us/core/STU7/ValueSet-detailed-race.html). A new OID has been assigned due to a slight change in scope: it includes the CDCREC code 2131-1 (Other Race) in place of the HL7 nullFlavor code "OTH" (Other). This version is intended to serve as the authoritative source for detailed race data going forward.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1496,7 +1492,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>20240606</v>
+        <v>20250724</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1518,11 +1514,7 @@
           <t>Family Member Value</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Added codes for maternal and paternal family relationships as well as mother in law and sister in law codes.</t>
-        </is>
-      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>StructureDefinition/us-core-familymemberhistory</t>
@@ -1609,7 +1601,7 @@
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>StructureDefinition/pediatric-bmi-for-age,StructureDefinition/us-core-pulse-oximetry,StructureDefinition/us-core-bmi,StructureDefinition/head-occipital-frontal-circumference-percentile,StructureDefinition/us-core-body-temperature,StructureDefinition/us-core-respiratory-rate,StructureDefinition/us-core-vital-signs,StructureDefinition/pediatric-weight-for-height,StructureDefinition/us-core-heart-rate,StructureDefinition/us-core-head-circumference,StructureDefinition/us-core-body-weight,StructureDefinition/us-core-body-height,StructureDefinition/us-core-blood-pressure</t>
+          <t>StructureDefinition/pediatric-bmi-for-age,StructureDefinition/us-core-pulse-oximetry,StructureDefinition/us-core-bmi,StructureDefinition/head-occipital-frontal-circumference-percentile,StructureDefinition/us-core-body-temperature,StructureDefinition/us-core-respiratory-rate,StructureDefinition/us-core-vital-signs,StructureDefinition/pediatric-weight-for-height,StructureDefinition/us-core-head-circumference,StructureDefinition/us-core-heart-rate,StructureDefinition/us-core-body-weight,StructureDefinition/us-core-body-height,StructureDefinition/us-core-blood-pressure</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1650,7 +1642,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>The HL7 OID used in the US Core Implementation Guide value set (http://hl7.org/fhir/us/core/ValueSet/omb-ethnicity-category) has been retained here, as the value set content is identical. However, the preferred reference is now the VSAC-hosted version, since both US Core and C-CDA will reference this set going forward</t>
+          <t>The HL7 OID used in the US Core Implementation Guide value set in US Core version 7.0 and prior (https://hl7.org/fhir/us/core/STU7/ValueSet-omb-race-category.html ) has been retained, as the value set content remains identical. However, the preferred reference going forward is the version hosted by VSAC, which serves as the authoritative source for both US Core and C-CDA.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1692,7 +1684,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>This value set was replicated from US Core's Detailed Ethnicity Set (http://hl7.org/fhir/us/core/ValueSet/detailed-ethnicity) and reuses the HL7 provided OID as it retains the same scope.</t>
+          <t>This value set is replicated from the US Core Detailed Ethnicity value set (http://hl7.org/fhir/us/core/ValueSet/detailed-ethnicity) and retains the same HL7-assigned OID, as its scope and members remain unchanged.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1734,7 +1726,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>The HL7 OID used in the US Core Implementation Guide value set (http://hl7.org/fhir/us/core/ValueSet/omb-ethnicity-category) has been retained here, as the value set content is identical. However, the preferred reference is now the VSAC-hosted version, since both US Core and C-CDA will reference this set going forward. Additionally, the US Core IG-based value set does not currently support expansion, making the VSAC version more suitable for implementation.</t>
+          <t>The OID for this value set, used in the US Core Implementation Guide version 7.0 and earlier (http://hl7.org/fhir/us/core/ValueSet/omb-ethnicity-category), has been retained. However, the VSAC-hosted version is now the preferred reference, as it serves as the authoritative source for both US Core and C-CDA and supports expansion for implementation.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2403,7 +2395,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-specimen,StructureDefinition/pediatric-bmi-for-age,StructureDefinition/us-core-pulse-oximetry,StructureDefinition/us-core-observation-pregnancyintent,StructureDefinition/us-core-procedure,StructureDefinition/head-occipital-frontal-circumference-percentile,StructureDefinition/us-core-observation-lab,StructureDefinition/us-core-bmi,StructureDefinition/us-core-vital-signs,StructureDefinition/us-core-servicerequest,StructureDefinition/us-core-simple-observation,StructureDefinition/us-core-pmo-servicerequest,StructureDefinition/us-core-heart-rate,StructureDefinition/us-core-head-circumference,StructureDefinition/us-core-body-height,StructureDefinition/us-core-smokingstatus,StructureDefinition/us-core-care-experience-preference,StructureDefinition/us-core-observation-clinical-result,StructureDefinition/us-core-respiratory-rate,StructureDefinition/us-core-body-temperature,StructureDefinition/us-core-observation-screening-assessment,StructureDefinition/us-core-condition-encounter-diagnosis,StructureDefinition/pediatric-weight-for-height,StructureDefinition/us-core-condition-problems-health-concerns,StructureDefinition/us-core-body-weight,StructureDefinition/us-core-observation-pregnancystatus,StructureDefinition/us-core-observation-occupation,StructureDefinition/us-core-average-blood-pressure,StructureDefinition/us-core-treatment-intervention-preference,StructureDefinition/us-core-observation-sexual-orientation,StructureDefinition/us-core-observation-adi-documentation,StructureDefinition/us-core-blood-pressure</t>
+          <t>StructureDefinition/us-core-specimen,StructureDefinition/pediatric-bmi-for-age,StructureDefinition/us-core-pulse-oximetry,StructureDefinition/us-core-observation-pregnancyintent,StructureDefinition/us-core-procedure,StructureDefinition/head-occipital-frontal-circumference-percentile,StructureDefinition/us-core-observation-lab,StructureDefinition/us-core-bmi,StructureDefinition/us-core-vital-signs,StructureDefinition/us-core-servicerequest,StructureDefinition/us-core-simple-observation,StructureDefinition/us-core-head-circumference,StructureDefinition/us-core-heart-rate,StructureDefinition/us-core-body-height,StructureDefinition/us-core-smokingstatus,StructureDefinition/us-core-care-experience-preference,StructureDefinition/us-core-observation-clinical-result,StructureDefinition/us-core-observation-screening-assessment,StructureDefinition/us-core-respiratory-rate,StructureDefinition/us-core-body-temperature,StructureDefinition/us-core-condition-encounter-diagnosis,StructureDefinition/us-core-condition-problems-health-concerns,StructureDefinition/pediatric-weight-for-height,StructureDefinition/us-core-observation-pregnancystatus,StructureDefinition/us-core-body-weight,StructureDefinition/us-core-observation-occupation,StructureDefinition/us-core-average-blood-pressure,StructureDefinition/us-core-treatment-intervention-preference,StructureDefinition/us-core-observation-adi-documentation,StructureDefinition/us-core-observation-sexual-orientation,StructureDefinition/us-core-blood-pressure</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3747,7 +3739,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>StructureDefinition/pediatric-bmi-for-age,StructureDefinition/us-core-pulse-oximetry,StructureDefinition/us-core-observation-pregnancyintent,StructureDefinition/head-occipital-frontal-circumference-percentile,StructureDefinition/us-core-observation-lab,StructureDefinition/us-core-bmi,StructureDefinition/us-core-vital-signs,StructureDefinition/us-core-simple-observation,StructureDefinition/us-core-heart-rate,StructureDefinition/us-core-head-circumference,StructureDefinition/us-core-body-height,StructureDefinition/us-core-smokingstatus,StructureDefinition/us-core-care-experience-preference,StructureDefinition/us-core-observation-clinical-result,StructureDefinition/us-core-respiratory-rate,StructureDefinition/us-core-body-temperature,StructureDefinition/us-core-observation-screening-assessment,StructureDefinition/pediatric-weight-for-height,StructureDefinition/us-core-body-weight,StructureDefinition/us-core-observation-pregnancystatus,StructureDefinition/us-core-observation-occupation,StructureDefinition/us-core-average-blood-pressure,StructureDefinition/us-core-treatment-intervention-preference,StructureDefinition/us-core-observation-sexual-orientation,StructureDefinition/us-core-observation-adi-documentation,StructureDefinition/us-core-blood-pressure</t>
+          <t>StructureDefinition/pediatric-bmi-for-age,StructureDefinition/us-core-pulse-oximetry,StructureDefinition/us-core-observation-pregnancyintent,StructureDefinition/head-occipital-frontal-circumference-percentile,StructureDefinition/us-core-observation-lab,StructureDefinition/us-core-bmi,StructureDefinition/us-core-vital-signs,StructureDefinition/us-core-simple-observation,StructureDefinition/us-core-head-circumference,StructureDefinition/us-core-heart-rate,StructureDefinition/us-core-body-height,StructureDefinition/us-core-smokingstatus,StructureDefinition/us-core-care-experience-preference,StructureDefinition/us-core-observation-clinical-result,StructureDefinition/us-core-observation-screening-assessment,StructureDefinition/us-core-respiratory-rate,StructureDefinition/us-core-body-temperature,StructureDefinition/pediatric-weight-for-height,StructureDefinition/us-core-observation-pregnancystatus,StructureDefinition/us-core-body-weight,StructureDefinition/us-core-observation-occupation,StructureDefinition/us-core-average-blood-pressure,StructureDefinition/us-core-treatment-intervention-preference,StructureDefinition/us-core-observation-adi-documentation,StructureDefinition/us-core-observation-sexual-orientation,StructureDefinition/us-core-blood-pressure</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5859,7 +5851,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-specimen,StructureDefinition/us-core-documentreference,StructureDefinition/us-core-observation-pregnancyintent,StructureDefinition/us-core-procedure,StructureDefinition/us-core-observation-lab,StructureDefinition/us-core-vital-signs,StructureDefinition/us-core-careplan,StructureDefinition/us-core-organization,StructureDefinition/us-core-adi-documentreference,StructureDefinition/us-core-pmo-servicerequest,StructureDefinition/us-core-practitioner,StructureDefinition/us-core-heart-rate,StructureDefinition/us-core-head-circumference,StructureDefinition/us-core-practitionerrole,StructureDefinition/us-core-smokingstatus,StructureDefinition/us-core-body-height,StructureDefinition/us-core-patient,StructureDefinition/us-core-provenance,StructureDefinition/us-core-observation-clinical-result,StructureDefinition/us-core-body-temperature,StructureDefinition/us-core-respiratory-rate,StructureDefinition/us-core-questionnaireresponse,StructureDefinition/us-core-condition-encounter-diagnosis,StructureDefinition/us-core-condition-problems-health-concerns,StructureDefinition/pediatric-weight-for-height,StructureDefinition/us-core-observation-pregnancystatus,StructureDefinition/us-core-medicationdispense,StructureDefinition/us-core-device,StructureDefinition/us-core-treatment-intervention-preference,StructureDefinition/pediatric-bmi-for-age,StructureDefinition/us-core-pulse-oximetry,StructureDefinition/us-core-diagnosticreport-lab,StructureDefinition/us-core-encounter,StructureDefinition/head-occipital-frontal-circumference-percentile,StructureDefinition/us-core-bmi,StructureDefinition/us-core-coverage,StructureDefinition/us-core-servicerequest,StructureDefinition/us-core-simple-observation,StructureDefinition/us-core-diagnosticreport-note,StructureDefinition/us-core-medicationrequest,StructureDefinition/us-core-medication,StructureDefinition/us-core-care-experience-preference,StructureDefinition/us-core-careteam,StructureDefinition/us-core-goal,StructureDefinition/us-core-observation-screening-assessment,StructureDefinition/us-core-familymemberhistory,StructureDefinition/us-core-immunization,StructureDefinition/us-core-relatedperson,StructureDefinition/us-core-body-weight,StructureDefinition/us-core-observation-occupation,StructureDefinition/us-core-average-blood-pressure,StructureDefinition/us-core-observation-sexual-orientation,StructureDefinition/us-core-observation-adi-documentation,StructureDefinition/us-core-location,StructureDefinition/us-core-allergyintolerance,StructureDefinition/us-core-blood-pressure</t>
+          <t>StructureDefinition/us-core-specimen,StructureDefinition/us-core-documentreference,StructureDefinition/us-core-observation-pregnancyintent,StructureDefinition/us-core-procedure,StructureDefinition/us-core-observation-lab,StructureDefinition/us-core-vital-signs,StructureDefinition/us-core-careplan,StructureDefinition/us-core-organization,StructureDefinition/us-core-adi-documentreference,StructureDefinition/us-core-head-circumference,StructureDefinition/us-core-heart-rate,StructureDefinition/us-core-practitioner,StructureDefinition/us-core-practitionerrole,StructureDefinition/us-core-body-height,StructureDefinition/us-core-smokingstatus,StructureDefinition/us-core-patient,StructureDefinition/us-core-provenance,StructureDefinition/us-core-observation-clinical-result,StructureDefinition/us-core-respiratory-rate,StructureDefinition/us-core-body-temperature,StructureDefinition/us-core-questionnaireresponse,StructureDefinition/us-core-condition-encounter-diagnosis,StructureDefinition/us-core-condition-problems-health-concerns,StructureDefinition/pediatric-weight-for-height,StructureDefinition/us-core-observation-pregnancystatus,StructureDefinition/us-core-medicationdispense,StructureDefinition/us-core-device,StructureDefinition/us-core-treatment-intervention-preference,StructureDefinition/pediatric-bmi-for-age,StructureDefinition/us-core-pulse-oximetry,StructureDefinition/us-core-diagnosticreport-lab,StructureDefinition/us-core-encounter,StructureDefinition/head-occipital-frontal-circumference-percentile,StructureDefinition/us-core-bmi,StructureDefinition/us-core-coverage,StructureDefinition/us-core-servicerequest,StructureDefinition/us-core-simple-observation,StructureDefinition/us-core-diagnosticreport-note,StructureDefinition/us-core-medicationrequest,StructureDefinition/us-core-medication,StructureDefinition/us-core-care-experience-preference,StructureDefinition/us-core-careteam,StructureDefinition/us-core-goal,StructureDefinition/us-core-observation-screening-assessment,StructureDefinition/us-core-immunization,StructureDefinition/us-core-familymemberhistory,StructureDefinition/us-core-relatedperson,StructureDefinition/us-core-body-weight,StructureDefinition/us-core-observation-occupation,StructureDefinition/us-core-average-blood-pressure,StructureDefinition/us-core-location,StructureDefinition/us-core-observation-adi-documentation,StructureDefinition/us-core-observation-sexual-orientation,StructureDefinition/us-core-allergyintolerance,StructureDefinition/us-core-blood-pressure</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -6195,7 +6187,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-pmo-servicerequest,StructureDefinition/us-core-medicationrequest,StructureDefinition/us-core-medicationdispense,StructureDefinition/us-core-servicerequest</t>
+          <t>StructureDefinition/us-core-medicationrequest,StructureDefinition/us-core-medicationdispense,StructureDefinition/us-core-servicerequest</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -6915,7 +6907,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>StructureDefinition/pediatric-bmi-for-age,StructureDefinition/us-core-pulse-oximetry,StructureDefinition/us-core-observation-pregnancyintent,StructureDefinition/us-core-bmi,StructureDefinition/us-core-observation-clinical-result,StructureDefinition/head-occipital-frontal-circumference-percentile,StructureDefinition/us-core-observation-lab,StructureDefinition/us-core-body-temperature,StructureDefinition/us-core-respiratory-rate,StructureDefinition/us-core-observation-screening-assessment,StructureDefinition/us-core-vital-signs,StructureDefinition/pediatric-weight-for-height,StructureDefinition/us-core-heart-rate,StructureDefinition/us-core-head-circumference,StructureDefinition/us-core-observation-pregnancystatus,StructureDefinition/us-core-body-weight,StructureDefinition/us-core-observation-occupation,StructureDefinition/us-core-average-blood-pressure,StructureDefinition/us-core-smokingstatus,StructureDefinition/us-core-body-height,StructureDefinition/us-core-observation-sexual-orientation,StructureDefinition/us-core-blood-pressure</t>
+          <t>StructureDefinition/pediatric-bmi-for-age,StructureDefinition/us-core-pulse-oximetry,StructureDefinition/us-core-observation-pregnancyintent,StructureDefinition/us-core-bmi,StructureDefinition/us-core-observation-clinical-result,StructureDefinition/head-occipital-frontal-circumference-percentile,StructureDefinition/us-core-observation-lab,StructureDefinition/us-core-observation-screening-assessment,StructureDefinition/us-core-body-temperature,StructureDefinition/us-core-respiratory-rate,StructureDefinition/us-core-vital-signs,StructureDefinition/pediatric-weight-for-height,StructureDefinition/us-core-head-circumference,StructureDefinition/us-core-heart-rate,StructureDefinition/us-core-observation-pregnancystatus,StructureDefinition/us-core-body-weight,StructureDefinition/us-core-observation-occupation,StructureDefinition/us-core-average-blood-pressure,StructureDefinition/us-core-body-height,StructureDefinition/us-core-smokingstatus,StructureDefinition/us-core-observation-sexual-orientation,StructureDefinition/us-core-blood-pressure</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -6963,7 +6955,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-care-experience-preference,StructureDefinition/us-core-goal,StructureDefinition/us-core-observation-pregnancyintent,StructureDefinition/us-core-observation-clinical-result,StructureDefinition/us-core-observation-lab,StructureDefinition/us-core-observation-screening-assessment,StructureDefinition/us-core-simple-observation,StructureDefinition/us-core-observation-pregnancystatus,StructureDefinition/us-core-observation-occupation,StructureDefinition/us-core-average-blood-pressure,StructureDefinition/us-core-treatment-intervention-preference,StructureDefinition/us-core-smokingstatus,StructureDefinition/us-core-observation-sexual-orientation,StructureDefinition/us-core-observation-adi-documentation</t>
+          <t>StructureDefinition/us-core-care-experience-preference,StructureDefinition/us-core-goal,StructureDefinition/us-core-observation-pregnancyintent,StructureDefinition/us-core-observation-clinical-result,StructureDefinition/us-core-observation-lab,StructureDefinition/us-core-observation-screening-assessment,StructureDefinition/us-core-simple-observation,StructureDefinition/us-core-observation-pregnancystatus,StructureDefinition/us-core-observation-occupation,StructureDefinition/us-core-average-blood-pressure,StructureDefinition/us-core-treatment-intervention-preference,StructureDefinition/us-core-smokingstatus,StructureDefinition/us-core-observation-adi-documentation,StructureDefinition/us-core-observation-sexual-orientation</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -7011,7 +7003,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>StructureDefinition/pediatric-bmi-for-age,StructureDefinition/us-core-pulse-oximetry,StructureDefinition/us-core-observation-pregnancyintent,StructureDefinition/head-occipital-frontal-circumference-percentile,StructureDefinition/us-core-observation-lab,StructureDefinition/us-core-bmi,StructureDefinition/us-core-vital-signs,StructureDefinition/us-core-simple-observation,StructureDefinition/us-core-heart-rate,StructureDefinition/us-core-head-circumference,StructureDefinition/us-core-body-height,StructureDefinition/us-core-smokingstatus,StructureDefinition/us-core-care-experience-preference,StructureDefinition/us-core-observation-clinical-result,StructureDefinition/us-core-respiratory-rate,StructureDefinition/us-core-body-temperature,StructureDefinition/us-core-observation-screening-assessment,StructureDefinition/pediatric-weight-for-height,StructureDefinition/us-core-body-weight,StructureDefinition/us-core-observation-pregnancystatus,StructureDefinition/us-core-observation-occupation,StructureDefinition/us-core-average-blood-pressure,StructureDefinition/us-core-treatment-intervention-preference,StructureDefinition/us-core-observation-sexual-orientation,StructureDefinition/us-core-observation-adi-documentation,StructureDefinition/us-core-blood-pressure</t>
+          <t>StructureDefinition/pediatric-bmi-for-age,StructureDefinition/us-core-pulse-oximetry,StructureDefinition/us-core-observation-pregnancyintent,StructureDefinition/head-occipital-frontal-circumference-percentile,StructureDefinition/us-core-observation-lab,StructureDefinition/us-core-bmi,StructureDefinition/us-core-vital-signs,StructureDefinition/us-core-simple-observation,StructureDefinition/us-core-head-circumference,StructureDefinition/us-core-heart-rate,StructureDefinition/us-core-body-height,StructureDefinition/us-core-smokingstatus,StructureDefinition/us-core-care-experience-preference,StructureDefinition/us-core-observation-clinical-result,StructureDefinition/us-core-observation-screening-assessment,StructureDefinition/us-core-respiratory-rate,StructureDefinition/us-core-body-temperature,StructureDefinition/pediatric-weight-for-height,StructureDefinition/us-core-observation-pregnancystatus,StructureDefinition/us-core-body-weight,StructureDefinition/us-core-observation-occupation,StructureDefinition/us-core-average-blood-pressure,StructureDefinition/us-core-treatment-intervention-preference,StructureDefinition/us-core-observation-adi-documentation,StructureDefinition/us-core-observation-sexual-orientation,StructureDefinition/us-core-blood-pressure</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -7059,7 +7051,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>StructureDefinition/pediatric-bmi-for-age,StructureDefinition/us-core-pulse-oximetry,StructureDefinition/us-core-observation-pregnancyintent,StructureDefinition/head-occipital-frontal-circumference-percentile,StructureDefinition/us-core-observation-lab,StructureDefinition/us-core-bmi,StructureDefinition/us-core-vital-signs,StructureDefinition/us-core-simple-observation,StructureDefinition/us-core-heart-rate,StructureDefinition/us-core-head-circumference,StructureDefinition/us-core-body-height,StructureDefinition/us-core-smokingstatus,StructureDefinition/us-core-care-experience-preference,StructureDefinition/us-core-observation-clinical-result,StructureDefinition/us-core-respiratory-rate,StructureDefinition/us-core-body-temperature,StructureDefinition/us-core-observation-screening-assessment,StructureDefinition/pediatric-weight-for-height,StructureDefinition/us-core-body-weight,StructureDefinition/us-core-observation-pregnancystatus,StructureDefinition/us-core-observation-occupation,StructureDefinition/us-core-average-blood-pressure,StructureDefinition/us-core-treatment-intervention-preference,StructureDefinition/us-core-observation-sexual-orientation,StructureDefinition/us-core-observation-adi-documentation,StructureDefinition/us-core-blood-pressure</t>
+          <t>StructureDefinition/pediatric-bmi-for-age,StructureDefinition/us-core-pulse-oximetry,StructureDefinition/us-core-observation-pregnancyintent,StructureDefinition/head-occipital-frontal-circumference-percentile,StructureDefinition/us-core-observation-lab,StructureDefinition/us-core-bmi,StructureDefinition/us-core-vital-signs,StructureDefinition/us-core-simple-observation,StructureDefinition/us-core-head-circumference,StructureDefinition/us-core-heart-rate,StructureDefinition/us-core-body-height,StructureDefinition/us-core-smokingstatus,StructureDefinition/us-core-care-experience-preference,StructureDefinition/us-core-observation-clinical-result,StructureDefinition/us-core-observation-screening-assessment,StructureDefinition/us-core-respiratory-rate,StructureDefinition/us-core-body-temperature,StructureDefinition/pediatric-weight-for-height,StructureDefinition/us-core-observation-pregnancystatus,StructureDefinition/us-core-body-weight,StructureDefinition/us-core-observation-occupation,StructureDefinition/us-core-average-blood-pressure,StructureDefinition/us-core-treatment-intervention-preference,StructureDefinition/us-core-observation-adi-documentation,StructureDefinition/us-core-observation-sexual-orientation,StructureDefinition/us-core-blood-pressure</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -7107,7 +7099,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>StructureDefinition/pediatric-bmi-for-age,StructureDefinition/us-core-pulse-oximetry,StructureDefinition/us-core-observation-pregnancyintent,StructureDefinition/head-occipital-frontal-circumference-percentile,StructureDefinition/us-core-observation-lab,StructureDefinition/us-core-bmi,StructureDefinition/us-core-vital-signs,StructureDefinition/us-core-simple-observation,StructureDefinition/us-core-heart-rate,StructureDefinition/us-core-head-circumference,StructureDefinition/us-core-body-height,StructureDefinition/us-core-care-experience-preference,StructureDefinition/us-core-observation-clinical-result,StructureDefinition/us-core-respiratory-rate,StructureDefinition/us-core-body-temperature,StructureDefinition/us-core-observation-screening-assessment,StructureDefinition/pediatric-weight-for-height,StructureDefinition/us-core-body-weight,StructureDefinition/us-core-observation-pregnancystatus,StructureDefinition/us-core-observation-occupation,StructureDefinition/us-core-average-blood-pressure,StructureDefinition/us-core-treatment-intervention-preference,StructureDefinition/us-core-observation-sexual-orientation,StructureDefinition/us-core-observation-adi-documentation,StructureDefinition/us-core-blood-pressure</t>
+          <t>StructureDefinition/pediatric-bmi-for-age,StructureDefinition/us-core-pulse-oximetry,StructureDefinition/us-core-observation-pregnancyintent,StructureDefinition/head-occipital-frontal-circumference-percentile,StructureDefinition/us-core-observation-lab,StructureDefinition/us-core-bmi,StructureDefinition/us-core-vital-signs,StructureDefinition/us-core-simple-observation,StructureDefinition/us-core-head-circumference,StructureDefinition/us-core-heart-rate,StructureDefinition/us-core-body-height,StructureDefinition/us-core-care-experience-preference,StructureDefinition/us-core-observation-clinical-result,StructureDefinition/us-core-observation-screening-assessment,StructureDefinition/us-core-respiratory-rate,StructureDefinition/us-core-body-temperature,StructureDefinition/pediatric-weight-for-height,StructureDefinition/us-core-observation-pregnancystatus,StructureDefinition/us-core-body-weight,StructureDefinition/us-core-observation-occupation,StructureDefinition/us-core-average-blood-pressure,StructureDefinition/us-core-treatment-intervention-preference,StructureDefinition/us-core-observation-adi-documentation,StructureDefinition/us-core-observation-sexual-orientation,StructureDefinition/us-core-blood-pressure</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -7203,7 +7195,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-pmo-servicerequest,StructureDefinition/us-core-servicerequest</t>
+          <t>StructureDefinition/us-core-servicerequest</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -7552,7 +7544,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/procedure-reason</t>
+          <t>http://hl7.org/fhir/ValueSet/provenance-activity-type</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -7567,32 +7559,32 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.3.432</t>
+          <t>2.16.840.1.113883.4.642.3.438</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>ProcedureReasonCodes</t>
+          <t>ProvenanceActivityType</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Procedure Reason Codes</t>
+          <t>Provenance activity type</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>This example value set defines the set of codes that can be used to indicate a reason for a procedure.</t>
+          <t>This value set contains representative Activity Type codes, which includes codes from the HL7 DocumentCompletion, ActStatus, and DataOperations code system, W3C PROV-DM and PROV-N concepts and display names, several HL7 Lifecycle Event codes for which there are agreed upon definitions, and non-duplicated codes from the HL7 Security and Privacy Ontology Operations codes.</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-pmo-servicerequest</t>
+          <t>StructureDefinition/us-core-provenance</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>SCT</t>
+          <t>THO (V3)</t>
         </is>
       </c>
       <c r="J154" t="inlineStr"/>
@@ -7600,7 +7592,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/provenance-activity-type</t>
+          <t>http://hl7.org/fhir/ValueSet/provenance-entity-role</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -7615,22 +7607,22 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.3.438</t>
+          <t>2.16.840.1.113883.4.642.3.436</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>ProvenanceActivityType</t>
+          <t>ProvenanceEntityRole</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Provenance activity type</t>
+          <t>ProvenanceEntityRole</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>This value set contains representative Activity Type codes, which includes codes from the HL7 DocumentCompletion, ActStatus, and DataOperations code system, W3C PROV-DM and PROV-N concepts and display names, several HL7 Lifecycle Event codes for which there are agreed upon definitions, and non-duplicated codes from the HL7 Security and Privacy Ontology Operations codes.</t>
+          <t>How an entity was used in an activity.</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -7640,7 +7632,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>THO (V3)</t>
+          <t>hl7.fhir.uv.xver-r5.r4</t>
         </is>
       </c>
       <c r="J155" t="inlineStr"/>
@@ -7648,7 +7640,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/provenance-entity-role</t>
+          <t>http://hl7.org/fhir/ValueSet/quantity-comparator</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -7658,32 +7650,32 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>active</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.3.436</t>
+          <t>2.16.840.1.113883.4.642.3.59</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>ProvenanceEntityRole</t>
+          <t>QuantityComparator</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>ProvenanceEntityRole</t>
+          <t>QuantityComparator</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>How an entity was used in an activity.</t>
+          <t>How the Quantity should be understood and represented.</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-provenance</t>
+          <t>StructureDefinition/pediatric-bmi-for-age,StructureDefinition/us-core-pulse-oximetry,StructureDefinition/us-core-bmi,StructureDefinition/head-occipital-frontal-circumference-percentile,StructureDefinition/us-core-body-temperature,StructureDefinition/us-core-respiratory-rate,StructureDefinition/pediatric-weight-for-height,StructureDefinition/us-core-head-circumference,StructureDefinition/us-core-heart-rate,StructureDefinition/us-core-body-weight,StructureDefinition/us-core-average-blood-pressure,StructureDefinition/us-core-body-height,StructureDefinition/us-core-blood-pressure</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -7696,7 +7688,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/quantity-comparator</t>
+          <t>http://hl7.org/fhir/ValueSet/questionnaire-answers</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -7706,37 +7698,37 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.3.59</t>
+          <t>2.16.840.1.113883.4.642.3.446</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>QuantityComparator</t>
+          <t>QuestionnaireAnswerCodes</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>QuantityComparator</t>
+          <t>Questionnaire Answer Codes</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>How the Quantity should be understood and represented.</t>
+          <t>Example list of codes for answers to questions. (Not complete or necessarily appropriate.)</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>StructureDefinition/pediatric-bmi-for-age,StructureDefinition/us-core-pulse-oximetry,StructureDefinition/us-core-bmi,StructureDefinition/head-occipital-frontal-circumference-percentile,StructureDefinition/us-core-body-temperature,StructureDefinition/us-core-respiratory-rate,StructureDefinition/pediatric-weight-for-height,StructureDefinition/us-core-heart-rate,StructureDefinition/us-core-head-circumference,StructureDefinition/us-core-body-weight,StructureDefinition/us-core-average-blood-pressure,StructureDefinition/us-core-body-height,StructureDefinition/us-core-blood-pressure</t>
+          <t>StructureDefinition/us-core-questionnaireresponse</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>hl7.fhir.uv.xver-r5.r4</t>
+          <t>SCT</t>
         </is>
       </c>
       <c r="J157" t="inlineStr"/>
@@ -7744,7 +7736,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/questionnaire-answers</t>
+          <t>http://hl7.org/fhir/ValueSet/questionnaire-answers-status</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -7759,22 +7751,22 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.3.446</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>QuestionnaireAnswerCodes</t>
+          <t>QuestionnaireResponseStatus</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Questionnaire Answer Codes</t>
+          <t>QuestionnaireResponseStatus</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Example list of codes for answers to questions. (Not complete or necessarily appropriate.)</t>
+          <t>Lifecycle status of the questionnaire response.</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -7784,7 +7776,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>SCT</t>
+          <t>hl7.fhir.uv.xver-r5.r4</t>
         </is>
       </c>
       <c r="J158" t="inlineStr"/>
@@ -7792,7 +7784,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/questionnaire-answers-status</t>
+          <t>http://hl7.org/fhir/ValueSet/reaction-event-severity</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -7807,27 +7799,27 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>2.16.840.1.113883.4.642.3.135</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>QuestionnaireResponseStatus</t>
+          <t>AllergyIntoleranceSeverity</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>QuestionnaireResponseStatus</t>
+          <t>AllergyIntoleranceSeverity</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Lifecycle status of the questionnaire response.</t>
+          <t>Clinical assessment of the severity of a reaction event as a whole, potentially considering multiple different manifestations.</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-questionnaireresponse</t>
+          <t>StructureDefinition/us-core-allergyintolerance</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -7840,7 +7832,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/reaction-event-severity</t>
+          <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -7855,32 +7847,32 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.3.135</t>
+          <t>2.16.840.1.113883.4.642.3.407</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AllergyIntoleranceSeverity</t>
+          <t>ObservationReferenceRangeAppliesToCodes</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>AllergyIntoleranceSeverity</t>
+          <t>Observation Reference Range Applies To Codes</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Clinical assessment of the severity of a reaction event as a whole, potentially considering multiple different manifestations.</t>
+          <t>This value set defines a set of codes that can be used to indicate the particular target population the reference range applies to.</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-allergyintolerance</t>
+          <t>StructureDefinition/pediatric-bmi-for-age,StructureDefinition/us-core-pulse-oximetry,StructureDefinition/us-core-observation-pregnancyintent,StructureDefinition/head-occipital-frontal-circumference-percentile,StructureDefinition/us-core-observation-lab,StructureDefinition/us-core-bmi,StructureDefinition/us-core-vital-signs,StructureDefinition/us-core-simple-observation,StructureDefinition/us-core-head-circumference,StructureDefinition/us-core-heart-rate,StructureDefinition/us-core-body-height,StructureDefinition/us-core-smokingstatus,StructureDefinition/us-core-care-experience-preference,StructureDefinition/us-core-observation-clinical-result,StructureDefinition/us-core-observation-screening-assessment,StructureDefinition/us-core-respiratory-rate,StructureDefinition/us-core-body-temperature,StructureDefinition/pediatric-weight-for-height,StructureDefinition/us-core-observation-pregnancystatus,StructureDefinition/us-core-body-weight,StructureDefinition/us-core-observation-occupation,StructureDefinition/us-core-average-blood-pressure,StructureDefinition/us-core-treatment-intervention-preference,StructureDefinition/us-core-observation-adi-documentation,StructureDefinition/us-core-observation-sexual-orientation,StructureDefinition/us-core-blood-pressure</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>hl7.fhir.uv.xver-r5.r4</t>
+          <t>SCT</t>
         </is>
       </c>
       <c r="J160" t="inlineStr"/>
@@ -7888,7 +7880,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+          <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -7903,32 +7895,32 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.3.407</t>
+          <t>2.16.840.1.113883.4.642.3.397</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>ObservationReferenceRangeAppliesToCodes</t>
+          <t>ObservationReferenceRangeMeaningCodes</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Observation Reference Range Applies To Codes</t>
+          <t>Observation Reference Range Meaning Codes</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>This value set defines a set of codes that can be used to indicate the particular target population the reference range applies to.</t>
+          <t>This value set defines a set of codes that can be used to indicate the meaning/use of a reference range for a particular target population.</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>StructureDefinition/pediatric-bmi-for-age,StructureDefinition/us-core-pulse-oximetry,StructureDefinition/us-core-observation-pregnancyintent,StructureDefinition/head-occipital-frontal-circumference-percentile,StructureDefinition/us-core-observation-lab,StructureDefinition/us-core-bmi,StructureDefinition/us-core-vital-signs,StructureDefinition/us-core-simple-observation,StructureDefinition/us-core-heart-rate,StructureDefinition/us-core-head-circumference,StructureDefinition/us-core-body-height,StructureDefinition/us-core-smokingstatus,StructureDefinition/us-core-care-experience-preference,StructureDefinition/us-core-observation-clinical-result,StructureDefinition/us-core-respiratory-rate,StructureDefinition/us-core-body-temperature,StructureDefinition/us-core-observation-screening-assessment,StructureDefinition/pediatric-weight-for-height,StructureDefinition/us-core-body-weight,StructureDefinition/us-core-observation-pregnancystatus,StructureDefinition/us-core-observation-occupation,StructureDefinition/us-core-average-blood-pressure,StructureDefinition/us-core-treatment-intervention-preference,StructureDefinition/us-core-observation-sexual-orientation,StructureDefinition/us-core-observation-adi-documentation,StructureDefinition/us-core-blood-pressure</t>
+          <t>StructureDefinition/pediatric-bmi-for-age,StructureDefinition/us-core-pulse-oximetry,StructureDefinition/us-core-observation-pregnancyintent,StructureDefinition/head-occipital-frontal-circumference-percentile,StructureDefinition/us-core-observation-lab,StructureDefinition/us-core-bmi,StructureDefinition/us-core-vital-signs,StructureDefinition/us-core-simple-observation,StructureDefinition/us-core-head-circumference,StructureDefinition/us-core-heart-rate,StructureDefinition/us-core-body-height,StructureDefinition/us-core-smokingstatus,StructureDefinition/us-core-care-experience-preference,StructureDefinition/us-core-observation-clinical-result,StructureDefinition/us-core-observation-screening-assessment,StructureDefinition/us-core-respiratory-rate,StructureDefinition/us-core-body-temperature,StructureDefinition/pediatric-weight-for-height,StructureDefinition/us-core-observation-pregnancystatus,StructureDefinition/us-core-body-weight,StructureDefinition/us-core-observation-occupation,StructureDefinition/us-core-average-blood-pressure,StructureDefinition/us-core-treatment-intervention-preference,StructureDefinition/us-core-observation-adi-documentation,StructureDefinition/us-core-observation-sexual-orientation,StructureDefinition/us-core-blood-pressure</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>SCT</t>
+          <t>THO</t>
         </is>
       </c>
       <c r="J161" t="inlineStr"/>
@@ -7936,7 +7928,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+          <t>http://hl7.org/fhir/ValueSet/relatedperson-relationshiptype</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -7951,32 +7943,32 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.3.397</t>
+          <t>2.16.840.1.113883.4.642.3.449</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>ObservationReferenceRangeMeaningCodes</t>
+          <t>PatientRelationshipType</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Observation Reference Range Meaning Codes</t>
+          <t>Patient relationship type</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>This value set defines a set of codes that can be used to indicate the meaning/use of a reference range for a particular target population.</t>
+          <t>A set of codes that can be used to indicate the relationship between a Patient and a Related Person.</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>StructureDefinition/pediatric-bmi-for-age,StructureDefinition/us-core-pulse-oximetry,StructureDefinition/us-core-observation-pregnancyintent,StructureDefinition/head-occipital-frontal-circumference-percentile,StructureDefinition/us-core-observation-lab,StructureDefinition/us-core-bmi,StructureDefinition/us-core-vital-signs,StructureDefinition/us-core-simple-observation,StructureDefinition/us-core-heart-rate,StructureDefinition/us-core-head-circumference,StructureDefinition/us-core-body-height,StructureDefinition/us-core-smokingstatus,StructureDefinition/us-core-care-experience-preference,StructureDefinition/us-core-observation-clinical-result,StructureDefinition/us-core-respiratory-rate,StructureDefinition/us-core-body-temperature,StructureDefinition/us-core-observation-screening-assessment,StructureDefinition/pediatric-weight-for-height,StructureDefinition/us-core-body-weight,StructureDefinition/us-core-observation-pregnancystatus,StructureDefinition/us-core-observation-occupation,StructureDefinition/us-core-average-blood-pressure,StructureDefinition/us-core-treatment-intervention-preference,StructureDefinition/us-core-observation-sexual-orientation,StructureDefinition/us-core-observation-adi-documentation,StructureDefinition/us-core-blood-pressure</t>
+          <t>StructureDefinition/us-core-relatedperson</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>THO</t>
+          <t>THO (V3),THO (V2)</t>
         </is>
       </c>
       <c r="J162" t="inlineStr"/>
@@ -7984,7 +7976,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/relatedperson-relationshiptype</t>
+          <t>http://hl7.org/fhir/ValueSet/request-intent</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -7999,32 +7991,32 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.3.449</t>
+          <t>2.16.840.1.113883.4.642.3.113</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>PatientRelationshipType</t>
+          <t>RequestIntent</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Patient relationship type</t>
+          <t>RequestIntent</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>A set of codes that can be used to indicate the relationship between a Patient and a Related Person.</t>
+          <t>Codes indicating the degree of authority/intentionality associated with a request.</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-relatedperson</t>
+          <t>StructureDefinition/us-core-servicerequest</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>THO (V3),THO (V2)</t>
+          <t>hl7.fhir.uv.xver-r5.r4</t>
         </is>
       </c>
       <c r="J163" t="inlineStr"/>
@@ -8032,7 +8024,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/request-intent</t>
+          <t>http://hl7.org/fhir/ValueSet/request-priority</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -8047,27 +8039,27 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.3.113</t>
+          <t>2.16.840.1.113883.4.642.3.115</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>RequestIntent</t>
+          <t>RequestPriority</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>RequestIntent</t>
+          <t>Request priority</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Codes indicating the degree of authority/intentionality associated with a request.</t>
+          <t>The clinical priority of a diagnostic order.</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-pmo-servicerequest,StructureDefinition/us-core-servicerequest</t>
+          <t>StructureDefinition/us-core-medicationrequest,StructureDefinition/us-core-servicerequest</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -8080,7 +8072,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/request-priority</t>
+          <t>http://hl7.org/fhir/ValueSet/request-status</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -8095,27 +8087,27 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.3.115</t>
+          <t>2.16.840.1.113883.4.642.3.111</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>RequestPriority</t>
+          <t>RequestStatus</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Request priority</t>
+          <t>RequestStatus</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>The clinical priority of a diagnostic order.</t>
+          <t>Codes identifying the lifecycle stage of a request.</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-pmo-servicerequest,StructureDefinition/us-core-medicationrequest,StructureDefinition/us-core-servicerequest</t>
+          <t>StructureDefinition/us-core-careplan,StructureDefinition/us-core-servicerequest</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -8128,7 +8120,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/request-status</t>
+          <t>http://hl7.org/fhir/ValueSet/resource-types</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -8138,37 +8130,37 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>active</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.3.111</t>
+          <t>2.16.840.1.113883.4.642.3.27</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>RequestStatus</t>
+          <t>ResourceType</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>RequestStatus</t>
+          <t>ResourceType</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Codes identifying the lifecycle stage of a request.</t>
+          <t>One of the resource types defined as part of this version of FHIR.</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-pmo-servicerequest,StructureDefinition/us-core-careplan,StructureDefinition/us-core-servicerequest</t>
+          <t>StructureDefinition/us-core-provenance</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>hl7.fhir.uv.xver-r5.r4</t>
+          <t>hl7.fhir.r4.core</t>
         </is>
       </c>
       <c r="J166" t="inlineStr"/>
@@ -8176,7 +8168,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+          <t>http://hl7.org/fhir/ValueSet/route-codes</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -8186,37 +8178,37 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.3.27</t>
+          <t>2.16.840.1.113883.4.642.3.98</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>ResourceType</t>
+          <t>SNOMEDCTRouteCodes</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>ResourceType</t>
+          <t>SNOMED CT Route Codes</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>One of the resource types defined as part of this version of FHIR.</t>
+          <t>This value set includes all Route codes from SNOMED CT - provided as an exemplar.</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-provenance</t>
+          <t>StructureDefinition/us-core-allergyintolerance</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>hl7.fhir.r4.core</t>
+          <t>SCT</t>
         </is>
       </c>
       <c r="J167" t="inlineStr"/>
@@ -8224,7 +8216,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/route-codes</t>
+          <t>http://hl7.org/fhir/ValueSet/security-labels</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -8234,45 +8226,41 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>active</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.3.98</t>
+          <t>2.16.840.1.113883.4.642.3.47</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>SNOMEDCTRouteCodes</t>
+          <t>All Security Labels</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>SNOMED CT Route Codes</t>
+          <t>SecurityLabels</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>This value set includes all Route codes from SNOMED CT - provided as an exemplar.</t>
+          <t>A single value set for all security labels defined by FHIR.</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-allergyintolerance</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>SCT</t>
-        </is>
-      </c>
+          <t>StructureDefinition/us-core-adi-documentreference,StructureDefinition/us-core-condition-problems-health-concerns,StructureDefinition/us-core-diagnosticreport-lab,StructureDefinition/us-core-documentreference,StructureDefinition/us-core-encounter,StructureDefinition/us-core-observation-lab</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+          <t>http://hl7.org/fhir/ValueSet/security-role-type</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -8282,41 +8270,45 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.3.47</t>
+          <t>2.16.840.1.113883.4.642.3.978</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>All Security Labels</t>
+          <t>SecurityRoleType</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>SecurityLabels</t>
+          <t>SecurityRoleType</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>A single value set for all security labels defined by FHIR.</t>
+          <t>This example FHIR value set is comprised of example Actor Type codes, which can be used to value FHIR agents, actors, and other role         elements such as those specified in financial transactions. The FHIR Actor value set is based on    DICOM Audit Message, C402;   ASTM Standard, E1762-95 [2013]; selected codes and          derived actor roles from HL7 RoleClass OID 2.16.840.1.113883.5.110;    HL7 Role Code 2.16.840.1.113883.5.111, including AgentRoleType;          HL7 ParticipationType OID: 2.16.840.1.113883.5.90; and    HL7 ParticipationFunction codes OID: 2.16.840.1.113883.5.88.           This value set includes, by reference, role codes from external code systems: NUCC Health Care Provider Taxonomy OID: 2.16.840.1.113883.6.101;          North American Industry Classification System [NAICS]OID: 2.16.840.1.113883.6.85; IndustryClassificationSystem 2.16.840.1.113883.1.11.16039;          and US Census Occupation Code OID: 2.16.840.1.113883.6.243 for relevant recipient or custodian codes not included in this value set.            If no source is indicated in the definition comments, then these are example FHIR codes.          It can be extended with appropriate roles described by SNOMED as well as those described in the HL7 Role Based Access Control Catalog and the          HL7 Healthcare (Security and Privacy) Access Control Catalog.            In Role-Based Access Control (RBAC), permissions are operations on an object that a user wishes to access. Permissions are grouped into roles.          A role characterizes the functions a user is allowed to perform. Roles are assigned to users. If the user's role has the appropriate permissions          to access an object, then that user is granted access to the object. FHIR readily enables RBAC, as FHIR Resources are object types and the CRUDE          events (the FHIR equivalent to permissions in the RBAC scheme) are operations on those objects.          In Attribute-Based Access Control (ABAC), a user requests to perform operations on objects. That user's access request is granted or denied          based on a set of access control policies that are specified in terms of attributes and conditions. FHIR readily enables ABAC, as instances of          a Resource in FHIR (again, Resources are object types) can have attributes associated with them. These attributes include security tags,          environment conditions, and a host of user and object characteristics, which are the same attributes as those used in ABAC. Attributes help          define the access control policies that determine the operations a user may perform on a Resource (in FHIR) or object (in ABAC). For example,          a tag (or attribute) may specify that the identified Resource (object) is not to be further disclosed without explicit consent from the patient.</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-adi-documentreference,StructureDefinition/us-core-condition-problems-health-concerns,StructureDefinition/us-core-diagnosticreport-lab,StructureDefinition/us-core-documentreference,StructureDefinition/us-core-encounter,StructureDefinition/us-core-observation-lab</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr"/>
+          <t>StructureDefinition/us-core-provenance</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>THO (V3),THO,DICOM</t>
+        </is>
+      </c>
       <c r="J169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/security-role-type</t>
+          <t>http://hl7.org/fhir/ValueSet/service-type</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -8331,32 +8323,32 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.3.978</t>
+          <t>2.16.840.1.113883.4.642.3.518</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>SecurityRoleType</t>
+          <t>ServiceType</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>SecurityRoleType</t>
+          <t>Service type</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>This example FHIR value set is comprised of example Actor Type codes, which can be used to value FHIR agents, actors, and other role         elements such as those specified in financial transactions. The FHIR Actor value set is based on    DICOM Audit Message, C402;   ASTM Standard, E1762-95 [2013]; selected codes and          derived actor roles from HL7 RoleClass OID 2.16.840.1.113883.5.110;    HL7 Role Code 2.16.840.1.113883.5.111, including AgentRoleType;          HL7 ParticipationType OID: 2.16.840.1.113883.5.90; and    HL7 ParticipationFunction codes OID: 2.16.840.1.113883.5.88.           This value set includes, by reference, role codes from external code systems: NUCC Health Care Provider Taxonomy OID: 2.16.840.1.113883.6.101;          North American Industry Classification System [NAICS]OID: 2.16.840.1.113883.6.85; IndustryClassificationSystem 2.16.840.1.113883.1.11.16039;          and US Census Occupation Code OID: 2.16.840.1.113883.6.243 for relevant recipient or custodian codes not included in this value set.            If no source is indicated in the definition comments, then these are example FHIR codes.          It can be extended with appropriate roles described by SNOMED as well as those described in the HL7 Role Based Access Control Catalog and the          HL7 Healthcare (Security and Privacy) Access Control Catalog.            In Role-Based Access Control (RBAC), permissions are operations on an object that a user wishes to access. Permissions are grouped into roles.          A role characterizes the functions a user is allowed to perform. Roles are assigned to users. If the user's role has the appropriate permissions          to access an object, then that user is granted access to the object. FHIR readily enables RBAC, as FHIR Resources are object types and the CRUDE          events (the FHIR equivalent to permissions in the RBAC scheme) are operations on those objects.          In Attribute-Based Access Control (ABAC), a user requests to perform operations on objects. That user's access request is granted or denied          based on a set of access control policies that are specified in terms of attributes and conditions. FHIR readily enables ABAC, as instances of          a Resource in FHIR (again, Resources are object types) can have attributes associated with them. These attributes include security tags,          environment conditions, and a host of user and object characteristics, which are the same attributes as those used in ABAC. Attributes help          define the access control policies that determine the operations a user may perform on a Resource (in FHIR) or object (in ABAC). For example,          a tag (or attribute) may specify that the identified Resource (object) is not to be further disclosed without explicit consent from the patient.</t>
+          <t>This value set defines an example set of codes of service-types.</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-provenance</t>
+          <t>StructureDefinition/us-core-encounter</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>THO (V3),THO,DICOM</t>
+          <t>THO</t>
         </is>
       </c>
       <c r="J170" t="inlineStr"/>
@@ -8364,7 +8356,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/service-type</t>
+          <t>http://hl7.org/fhir/ValueSet/servicerequest-category</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -8379,32 +8371,32 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.3.518</t>
+          <t>2.16.840.1.113883.4.642.3.434</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>ServiceType</t>
+          <t>ServiceRequestCategoryCodes</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Service type</t>
+          <t>Service Request Category Codes</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>This value set defines an example set of codes of service-types.</t>
+          <t>An example value set of SNOMED CT concepts that can classify a requested service</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-encounter</t>
+          <t>ValueSet/us-core-servicerequest-category,StructureDefinition/us-core-servicerequest</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>THO</t>
+          <t>SCT</t>
         </is>
       </c>
       <c r="J171" t="inlineStr"/>
@@ -8412,7 +8404,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/servicerequest-category</t>
+          <t>http://hl7.org/fhir/ValueSet/servicerequest-orderdetail</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -8427,27 +8419,27 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.3.434</t>
+          <t>2.16.840.1.113883.4.642.3.435</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>ServiceRequestCategoryCodes</t>
+          <t>ServiceRequestOrderDetailsCodes</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Service Request Category Codes</t>
+          <t>Service Request Order Details Codes</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>An example value set of SNOMED CT concepts that can classify a requested service</t>
+          <t>An example value set of Codified order entry details concepts.  These concepts only make sense in the context of what is being ordered.  This example is for a patient ventilation order</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-pmo-servicerequest,ValueSet/us-core-servicerequest-category,StructureDefinition/us-core-servicerequest</t>
+          <t>StructureDefinition/us-core-servicerequest</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -8460,7 +8452,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/servicerequest-orderdetail</t>
+          <t>http://hl7.org/fhir/ValueSet/specimen-collection-method</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -8475,27 +8467,27 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.3.435</t>
+          <t>2.16.840.1.113883.4.642.3.468</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>ServiceRequestOrderDetailsCodes</t>
+          <t>FHIRSpecimenCollectionMethod</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Service Request Order Details Codes</t>
+          <t>FHIR Specimen Collection Method</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>An example value set of Codified order entry details concepts.  These concepts only make sense in the context of what is being ordered.  This example is for a patient ventilation order</t>
+          <t xml:space="preserve"> This example value set defines a set of codes that can be used to indicate the method by which a specimen was collected.</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-pmo-servicerequest,StructureDefinition/us-core-servicerequest</t>
+          <t>StructureDefinition/us-core-specimen</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -8508,7 +8500,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/specimen-collection-method</t>
+          <t>http://hl7.org/fhir/ValueSet/specimen-container-type</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -8523,22 +8515,22 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.3.468</t>
+          <t>2.16.840.1.113883.4.642.3.470</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>FHIRSpecimenCollectionMethod</t>
+          <t>SpecimenContainerType</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>FHIR Specimen Collection Method</t>
+          <t>Specimen Container Type</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve"> This example value set defines a set of codes that can be used to indicate the method by which a specimen was collected.</t>
+          <t>Checks on the patient prior specimen collection. All SNOMED CT concepts descendants of 706041008 |Device for body fluid and tissue collection/transfer/processing (physical object)|</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -8556,7 +8548,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/specimen-container-type</t>
+          <t>http://hl7.org/fhir/ValueSet/specimen-processing-procedure</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -8571,22 +8563,22 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.3.470</t>
+          <t>2.16.840.1.113883.4.642.3.469</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>SpecimenContainerType</t>
+          <t>SpecimenProcessingProcedure</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Specimen Container Type</t>
+          <t>Specimen processing procedure</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Checks on the patient prior specimen collection. All SNOMED CT concepts descendants of 706041008 |Device for body fluid and tissue collection/transfer/processing (physical object)|</t>
+          <t>The technique that is used to perform the process or preserve the specimen.</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -8596,7 +8588,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>SCT</t>
+          <t>THO (V2)</t>
         </is>
       </c>
       <c r="J175" t="inlineStr"/>
@@ -8604,7 +8596,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/specimen-processing-procedure</t>
+          <t>http://hl7.org/fhir/ValueSet/specimen-status</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -8619,22 +8611,22 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.3.469</t>
+          <t>2.16.840.1.113883.4.642.3.471</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>SpecimenProcessingProcedure</t>
+          <t>SpecimenStatus</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Specimen processing procedure</t>
+          <t>SpecimenStatus</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>The technique that is used to perform the process or preserve the specimen.</t>
+          <t>Codes providing the status/availability of a specimen.</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -8644,7 +8636,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>THO (V2)</t>
+          <t>hl7.fhir.uv.xver-r5.r4</t>
         </is>
       </c>
       <c r="J176" t="inlineStr"/>
@@ -8652,7 +8644,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/specimen-status</t>
+          <t>http://hl7.org/fhir/ValueSet/subscriber-relationship</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -8667,32 +8659,32 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.3.471</t>
+          <t>2.16.840.1.113883.4.642.3.1385</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>SpecimenStatus</t>
+          <t>SubscriberRelationshipCodes</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>SpecimenStatus</t>
+          <t>SubscriberPolicyholder Relationship Codes</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Codes providing the status/availability of a specimen.</t>
+          <t>This value set includes codes for the relationship between the Subscriber and the Beneficiary (insured/covered party/patient).</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-specimen</t>
+          <t>StructureDefinition/us-core-coverage</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>hl7.fhir.uv.xver-r5.r4</t>
+          <t>THO</t>
         </is>
       </c>
       <c r="J177" t="inlineStr"/>
@@ -8700,7 +8692,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/subscriber-relationship</t>
+          <t>http://hl7.org/fhir/ValueSet/substance-code</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -8715,32 +8707,32 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.3.1385</t>
+          <t>2.16.840.1.113883.4.642.3.473</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>SubscriberRelationshipCodes</t>
+          <t>SubstanceCode</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>SubscriberPolicyholder Relationship Codes</t>
+          <t>Substance Code</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>This value set includes codes for the relationship between the Subscriber and the Beneficiary (insured/covered party/patient).</t>
+          <t>This value set contains concept codes for specific substances. It includes codes from [SNOMED](http://snomed.info/sct) where concept is-a 105590001 (Substance (substance)) and where concept is-a 373873005 (Pharmaceutical / biologic product (product))</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-coverage</t>
+          <t>StructureDefinition/us-core-allergyintolerance</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>THO</t>
+          <t>SCT</t>
         </is>
       </c>
       <c r="J178" t="inlineStr"/>
@@ -8748,7 +8740,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/substance-code</t>
+          <t>http://hl7.org/fhir/ValueSet/ucum-bodylength</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -8763,32 +8755,32 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.3.473</t>
+          <t>2.16.840.1.113883.4.642.3.958</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>SubstanceCode</t>
+          <t>BodyLengthUnits</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Substance Code</t>
+          <t>Body Length Units</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>This value set contains concept codes for specific substances. It includes codes from [SNOMED](http://snomed.info/sct) where concept is-a 105590001 (Substance (substance)) and where concept is-a 373873005 (Pharmaceutical / biologic product (product))</t>
+          <t>UCUM units for recording body length measures such as height and head circumference</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-allergyintolerance</t>
+          <t>StructureDefinition/us-core-head-circumference,StructureDefinition/us-core-body-height</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>SCT</t>
+          <t>UCUM</t>
         </is>
       </c>
       <c r="J179" t="inlineStr"/>
@@ -8796,7 +8788,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/ucum-bodylength</t>
+          <t>http://hl7.org/fhir/ValueSet/ucum-bodytemp</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -8811,27 +8803,27 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.3.958</t>
+          <t>2.16.840.1.113883.4.642.3.957</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>BodyLengthUnits</t>
+          <t>BodyTemperatureUnits</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Body Length Units</t>
+          <t>Body Temperature Units</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>UCUM units for recording body length measures such as height and head circumference</t>
+          <t>UCUM units for recording Body Temperature</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-head-circumference,StructureDefinition/us-core-body-height</t>
+          <t>StructureDefinition/us-core-body-temperature</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -8844,7 +8836,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/ucum-bodytemp</t>
+          <t>http://hl7.org/fhir/ValueSet/ucum-bodyweight</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -8859,27 +8851,27 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.3.957</t>
+          <t>2.16.840.1.113883.4.642.3.956</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>BodyTemperatureUnits</t>
+          <t>BodyWeightUnits</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Body Temperature Units</t>
+          <t>Body Weight Units</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>UCUM units for recording Body Temperature</t>
+          <t>UCUM units for recording Body Weight</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-body-temperature</t>
+          <t>StructureDefinition/us-core-body-weight</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -8892,7 +8884,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/ucum-bodyweight</t>
+          <t>http://hl7.org/fhir/ValueSet/ucum-common</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -8905,29 +8897,21 @@
           <t>draft</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>2.16.840.1.113883.4.642.3.956</t>
-        </is>
-      </c>
+      <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr">
         <is>
-          <t>BodyWeightUnits</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>Body Weight Units</t>
-        </is>
-      </c>
+          <t>Common UCUM units</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr"/>
       <c r="G182" t="inlineStr">
         <is>
-          <t>UCUM units for recording Body Weight</t>
+          <t>Commonly encountered UCUM units (for purposes of helping populate look ups.</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-body-weight</t>
+          <t>StructureDefinition/us-core-medicationrequest,StructureDefinition/us-core-medicationdispense</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -8940,7 +8924,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/ucum-common</t>
+          <t>http://hl7.org/fhir/ValueSet/ucum-vitals-common</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -8953,21 +8937,29 @@
           <t>draft</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>2.16.840.1.113883.4.642.3.955</t>
+        </is>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Common UCUM units</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr"/>
+          <t>VitalSignsUnits</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Vital Signs Units</t>
+        </is>
+      </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Commonly encountered UCUM units (for purposes of helping populate look ups.</t>
+          <t>Common UCUM units for recording Vital Signs</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-medicationrequest,StructureDefinition/us-core-medicationdispense</t>
+          <t>StructureDefinition/pediatric-bmi-for-age,StructureDefinition/us-core-pulse-oximetry,StructureDefinition/us-core-bmi,StructureDefinition/head-occipital-frontal-circumference-percentile,StructureDefinition/us-core-body-temperature,StructureDefinition/us-core-respiratory-rate,StructureDefinition/us-core-vital-signs,StructureDefinition/pediatric-weight-for-height,StructureDefinition/us-core-head-circumference,StructureDefinition/us-core-heart-rate,StructureDefinition/us-core-body-weight,StructureDefinition/us-core-body-height,StructureDefinition/us-core-blood-pressure</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -8980,7 +8972,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/ucum-vitals-common</t>
+          <t>http://hl7.org/fhir/ValueSet/udi-entry-type</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -8995,32 +8987,32 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.3.955</t>
+          <t>2.16.840.1.113883.4.642.3.211</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>VitalSignsUnits</t>
+          <t>UDIEntryType</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Vital Signs Units</t>
+          <t>UDIEntryType</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Common UCUM units for recording Vital Signs</t>
+          <t>Codes to identify how UDI data was entered.</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>StructureDefinition/pediatric-bmi-for-age,StructureDefinition/us-core-pulse-oximetry,StructureDefinition/us-core-bmi,StructureDefinition/head-occipital-frontal-circumference-percentile,StructureDefinition/us-core-body-temperature,StructureDefinition/us-core-respiratory-rate,StructureDefinition/us-core-vital-signs,StructureDefinition/pediatric-weight-for-height,StructureDefinition/us-core-heart-rate,StructureDefinition/us-core-head-circumference,StructureDefinition/us-core-body-weight,StructureDefinition/us-core-body-height,StructureDefinition/us-core-blood-pressure</t>
+          <t>StructureDefinition/us-core-device</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>UCUM</t>
+          <t>hl7.fhir.uv.xver-r5.r4</t>
         </is>
       </c>
       <c r="J184" t="inlineStr"/>
@@ -9028,47 +9020,43 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/udi-entry-type</t>
+          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-clinical-note-type</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>4.0.1</t>
+          <t>9.0.0</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>active</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.3.211</t>
+          <t>2.16.840.1.113883.4.642.40.2.48.1</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>UDIEntryType</t>
+          <t>USCoreClinicalNoteType</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>UDIEntryType</t>
+          <t>US Core Clinical Note Type</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Codes to identify how UDI data was entered.</t>
-        </is>
-      </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>StructureDefinition/us-core-device</t>
-        </is>
-      </c>
+          <t>The US Core Clinical Note Type Value Set is a 'starter set' of types supported for fetching and storing clinical notes.</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr">
         <is>
-          <t>hl7.fhir.uv.xver-r5.r4</t>
+          <t>LOINC</t>
         </is>
       </c>
       <c r="J185" t="inlineStr"/>
@@ -9076,12 +9064,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-clinical-note-type</t>
+          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-clinical-result-observation-category</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>9.0.0-ballot</t>
+          <t>9.0.0</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -9091,28 +9079,32 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.40.2.48.1</t>
+          <t>2.16.840.1.113883.4.642.40.2.48.2</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>USCoreClinicalNoteType</t>
+          <t>USCoreClinicalResultObservationCategory</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>US Core Clinical Note Type</t>
+          <t>US Core Clinical Result Observation Category</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>The US Core Clinical Note Type Value Set is a 'starter set' of types supported for fetching and storing clinical notes.</t>
-        </is>
-      </c>
-      <c r="H186" t="inlineStr"/>
+          <t>Used to classify the context of clinical result observations.</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>StructureDefinition/us-core-observation-lab,StructureDefinition/us-core-observation-clinical-result</t>
+        </is>
+      </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>LOINC</t>
+          <t>THO</t>
         </is>
       </c>
       <c r="J186" t="inlineStr"/>
@@ -9120,12 +9112,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-clinical-result-observation-category</t>
+          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-condition-code</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>9.0.0-ballot</t>
+          <t>9.0.0</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -9135,32 +9127,32 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.40.2.48.2</t>
+          <t>2.16.840.1.113883.4.642.40.2.48.15</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>USCoreClinicalResultObservationCategory</t>
+          <t>USCoreConditionCodes</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>US Core Clinical Result Observation Category</t>
+          <t>US Core Condition Codes</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Used to classify the context of clinical result observations.</t>
+          <t>This describes the problem. Diagnosis/Problem List is broadly defined as a series of brief statements that catalog a patient's medical, nursing, dental, social, preventative and psychiatric events and issues that are relevant to that patient's healthcare (e.g., signs, symptoms, and defined conditions). ICD-10 is appropriate for Diagnosis information, and ICD-9 for historical information.</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-observation-lab,StructureDefinition/us-core-observation-clinical-result</t>
+          <t>StructureDefinition/us-core-condition-problems-health-concerns,StructureDefinition/us-core-medicationrequest,StructureDefinition/us-core-procedure,StructureDefinition/us-core-servicerequest,StructureDefinition/us-core-familymemberhistory,StructureDefinition/us-core-condition-encounter-diagnosis</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>THO</t>
+          <t>SCT,hl7.terminology.r4</t>
         </is>
       </c>
       <c r="J187" t="inlineStr"/>
@@ -9168,12 +9160,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-condition-code</t>
+          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-condition-code-current</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>9.0.0-ballot</t>
+          <t>9.0.0</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -9183,27 +9175,27 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.40.2.48.15</t>
+          <t>2.16.840.1.113883.4.642.40.2.48.3</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>USCoreConditionCodes</t>
+          <t>USCoreConditionCodesCurrent</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>US Core Condition Codes</t>
+          <t>US Core Condition Codes Current</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>This describes the problem. Diagnosis/Problem List is broadly defined as a series of brief statements that catalog a patient's medical, nursing, dental, social, preventative and psychiatric events and issues that are relevant to that patient's healthcare (e.g., signs, symptoms, and defined conditions). ICD-10 is appropriate for Diagnosis information, and ICD-9 for historical information.</t>
+          <t>This valueset is defined the same as the [US Core Condition Codes](ValueSet-us-core-condition-code.html) value set except it excludes ICD-9-CM codes. It us used for encoding newly recorded, non-legacy problem list items, health concerns and diagnosis using SNOMED CT and ICD-10-CM per USCDI requirements.</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-medicationrequest,StructureDefinition/us-core-condition-problems-health-concerns,StructureDefinition/us-core-procedure,StructureDefinition/us-core-servicerequest,StructureDefinition/us-core-condition-encounter-diagnosis,StructureDefinition/us-core-familymemberhistory</t>
+          <t>StructureDefinition/us-core-condition-problems-health-concerns,StructureDefinition/us-core-condition-encounter-diagnosis</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -9216,12 +9208,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-condition-code-current</t>
+          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-diagnosticreport-category</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>9.0.0-ballot</t>
+          <t>9.0.0</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -9231,32 +9223,32 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.40.2.48.3</t>
+          <t>2.16.840.1.113883.4.642.40.2.48.4</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>USCoreConditionCodesCurrent</t>
+          <t>USCoreDiagnosticReportCategory</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>US Core Condition Codes Current</t>
+          <t>US Core Diagnostic Report Category Codes</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>This valueset is defined the same as the [US Core Condition Codes](ValueSet-us-core-condition-code.html) value set except it excludes ICD-9-CM codes. It us used for encoding newly recorded, non-legacy problem list items, health concerns and diagnosis using SNOMED CT and ICD-10-CM per USCDI requirements.</t>
+          <t>The US Core Diagnostic Report Category Value Set is a 'starter set' of categories supported for fetching and Diagnostic Reports and notes.</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-condition-problems-health-concerns,StructureDefinition/us-core-condition-encounter-diagnosis</t>
+          <t>StructureDefinition/us-core-diagnosticreport-note</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>SCT,hl7.terminology.r4</t>
+          <t>LOINC</t>
         </is>
       </c>
       <c r="J189" t="inlineStr"/>
@@ -9264,12 +9256,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-diagnosticreport-category</t>
+          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-diagnosticreport-report-and-note-codes</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>9.0.0-ballot</t>
+          <t>9.0.0</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -9279,22 +9271,22 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.40.2.48.4</t>
+          <t>2.16.840.1.113883.4.642.40.2.48.5</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>USCoreDiagnosticReportCategory</t>
+          <t>USCoreNonLaboratoryCodes</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>US Core Diagnostic Report Category Codes</t>
+          <t>US Core Non Laboratory Codes</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>The US Core Diagnostic Report Category Value Set is a 'starter set' of categories supported for fetching and Diagnostic Reports and notes.</t>
+          <t>This value set includes All LOINC codes defined as type "clinical," therefore excluding laboratory tests, survey instruments, and claims documents. This includes observables such as vital signs, hemodynamics, intake/output, EKG, obstetric ultrasound, and cardiac echo, and includes discrete and narrative diagnostic observations and reports.</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -9312,12 +9304,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-diagnosticreport-report-and-note-codes</t>
+          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-documentreference-category</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>9.0.0-ballot</t>
+          <t>9.0.0</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -9327,32 +9319,32 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.40.2.48.5</t>
+          <t>2.16.840.1.113883.4.642.40.2.48.6</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>USCoreNonLaboratoryCodes</t>
+          <t>USCoreDocumentReferenceCategory</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>US Core Non Laboratory Codes</t>
+          <t>US Core DocumentReference Category</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>This value set includes All LOINC codes defined as type "clinical," therefore excluding laboratory tests, survey instruments, and claims documents. This includes observables such as vital signs, hemodynamics, intake/output, EKG, obstetric ultrasound, and cardiac echo, and includes discrete and narrative diagnostic observations and reports.</t>
+          <t>The US Core DocumentReferences Category Value Set is a 'starter set' of categories supported for fetching and storing clinical notes.</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-diagnosticreport-note</t>
+          <t>StructureDefinition/us-core-documentreference</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>LOINC</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="J191" t="inlineStr"/>
@@ -9360,12 +9352,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-documentreference-category</t>
+          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-documentreference-type</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>9.0.0-ballot</t>
+          <t>9.0.0</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -9375,22 +9367,22 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.40.2.48.6</t>
+          <t>2.16.840.1.113883.4.642.40.2.48.7</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>USCoreDocumentReferenceCategory</t>
+          <t>USCoreDocumentReferenceType</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>US Core DocumentReference Category</t>
+          <t>US Core DocumentReference Type</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>The US Core DocumentReferences Category Value Set is a 'starter set' of categories supported for fetching and storing clinical notes.</t>
+          <t>The US Core DocumentReference Type Value Set includes all LOINC values whose SCALE is "Doc" in the LOINC database and the HL7 v3 Code System NullFlavor concept 'unknown'</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -9400,7 +9392,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>THO (V3),LOINC</t>
         </is>
       </c>
       <c r="J192" t="inlineStr"/>
@@ -9408,12 +9400,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-documentreference-type</t>
+          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-goal-description</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>9.0.0-ballot</t>
+          <t>9.0.0</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -9423,32 +9415,32 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.40.2.48.7</t>
+          <t>2.16.840.1.113883.4.642.40.2.48.16</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>USCoreDocumentReferenceType</t>
+          <t>USCoreGoalCodes</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>US Core DocumentReference Type</t>
+          <t>US Core Goal Codes</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>The US Core DocumentReference Type Value Set includes all LOINC values whose SCALE is "Doc" in the LOINC database and the HL7 v3 Code System NullFlavor concept 'unknown'</t>
+          <t>Concepts from SNOMED CT  and LOINC code systems that can be used to indicate the goal.</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-documentreference</t>
+          <t>StructureDefinition/us-core-goal</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>THO (V3),LOINC</t>
+          <t>SCT,LOINC</t>
         </is>
       </c>
       <c r="J193" t="inlineStr"/>
@@ -9456,12 +9448,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-goal-description</t>
+          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-laboratory-test-codes</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>9.0.0-ballot</t>
+          <t>9.0.0</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -9471,32 +9463,32 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.40.2.48.16</t>
+          <t>2.16.840.1.113883.4.642.40.2.48.17</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>USCoreGoalCodes</t>
+          <t>USCoreLaboratoryTestCodes</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>US Core Goal Codes</t>
+          <t>US Core Laboratory Test Codes</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Concepts from SNOMED CT  and LOINC code systems that can be used to indicate the goal.</t>
+          <t>Laboratory LOINC codes: From the introduction to August 2022 LOINC Users' guide; "The current scope of the existing laboratory portion of the LOINC  database includes all observations reported by clinical laboratories, including the specialty areas: chemistry, including therapeutic drug monitoring and toxicology; hematology; serology; blood bank; microbiology; cytology; surgical pathology; and fertility.</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-goal</t>
+          <t>StructureDefinition/us-core-diagnosticreport-lab,StructureDefinition/us-core-observation-lab</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>SCT,LOINC</t>
+          <t>LOINC</t>
         </is>
       </c>
       <c r="J194" t="inlineStr"/>
@@ -9504,12 +9496,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-laboratory-test-codes</t>
+          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-narrative-status</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>9.0.0-ballot</t>
+          <t>9.0.0</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -9519,32 +9511,32 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.40.2.48.17</t>
+          <t>2.16.840.1.113883.4.642.40.2.48.8</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>USCoreLaboratoryTestCodes</t>
+          <t>NarrativeStatus</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>US Core Laboratory Test Codes</t>
+          <t>US Core Narrative Status</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Laboratory LOINC codes: From the introduction to August 2022 LOINC Users' guide; "The current scope of the existing laboratory portion of the LOINC  database includes all observations reported by clinical laboratories, including the specialty areas: chemistry, including therapeutic drug monitoring and toxicology; hematology; serology; blood bank; microbiology; cytology; surgical pathology; and fertility.</t>
+          <t>The US Core Narrative Status Value Set limits the text status for the resource narrative.</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-diagnosticreport-lab,StructureDefinition/us-core-observation-lab</t>
+          <t>StructureDefinition/us-core-careplan</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>LOINC</t>
+          <t>hl7.fhir.uv.xver-r5.r4</t>
         </is>
       </c>
       <c r="J195" t="inlineStr"/>
@@ -9552,12 +9544,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-narrative-status</t>
+          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-observation-smoking-status-status</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>9.0.0-ballot</t>
+          <t>9.0.0</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -9567,27 +9559,27 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.40.2.48.8</t>
+          <t>2.16.840.1.113883.4.642.40.2.48.9</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>NarrativeStatus</t>
+          <t>USCoreObservationSmokingStatusStatus</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>US Core Narrative Status</t>
+          <t>US Core Status for Smoking Status Observation</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>The US Core Narrative Status Value Set limits the text status for the resource narrative.</t>
+          <t>Codes providing the status of an observation for smoking status. Constrained to `final`and `entered-in-error`.</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-careplan</t>
+          <t>StructureDefinition/us-core-smokingstatus</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -9600,12 +9592,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-observation-smoking-status-status</t>
+          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-problem-or-health-concern</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>9.0.0-ballot</t>
+          <t>9.0.0</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -9615,32 +9607,32 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.40.2.48.9</t>
+          <t>2.16.840.1.113883.4.642.40.2.48.18</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>USCoreObservationSmokingStatusStatus</t>
+          <t>USCoreProblemOrHealthConcern</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>US Core Status for Smoking Status Observation</t>
+          <t>US Core Problem or Health Concern</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Codes providing the status of an observation for smoking status. Constrained to `final`and `entered-in-error`.</t>
+          <t>Code set for category codes for *US Core Condition Problems and Health Concerns Profile* consisting of the concepts "problem" and "health-concern".</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-smokingstatus</t>
+          <t>StructureDefinition/us-core-condition-problems-health-concerns</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>hl7.fhir.uv.xver-r5.r4</t>
+          <t>Internal,THO</t>
         </is>
       </c>
       <c r="J197" t="inlineStr"/>
@@ -9648,12 +9640,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-problem-or-health-concern</t>
+          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-procedure-code</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>9.0.0-ballot</t>
+          <t>9.0.0</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -9663,32 +9655,32 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.40.2.48.18</t>
+          <t>2.16.840.1.113883.4.642.40.2.48.19</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>USCoreProblemOrHealthConcern</t>
+          <t>USCoreProcedureCodes</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>US Core Problem or Health Concern</t>
+          <t>US Core Procedure Codes</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Code set for category codes for *US Core Condition Problems and Health Concerns Profile* consisting of the concepts "problem" and "health-concern".</t>
+          <t>Concepts from CPT, SNOMED CT, HCPCS Level II Alphanumeric Codes, ICD-10-PCS,CDT and LOINC code systems that can be used to indicate the type of procedure performed.</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-condition-problems-health-concerns</t>
+          <t>StructureDefinition/us-core-procedure,StructureDefinition/us-core-servicerequest</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>Internal,THO</t>
+          <t>SCT,LOINC,hl7.terminology.r4</t>
         </is>
       </c>
       <c r="J198" t="inlineStr"/>
@@ -9696,12 +9688,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-procedure-code</t>
+          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-screening-assessment-condition-category</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>9.0.0-ballot</t>
+          <t>9.0.0</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -9711,32 +9703,28 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.40.2.48.19</t>
+          <t>2.16.840.1.113883.4.642.40.2.48.10</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>USCoreProcedureCodes</t>
+          <t>USCoreScreeningAssessmentConditionCategory</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>US Core Procedure Codes</t>
+          <t>US Core Screening Assessment Condition Category</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Concepts from CPT, SNOMED CT, HCPCS Level II Alphanumeric Codes, ICD-10-PCS,CDT and LOINC code systems that can be used to indicate the type of procedure performed.</t>
-        </is>
-      </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>StructureDefinition/us-core-procedure,StructureDefinition/us-core-servicerequest</t>
-        </is>
-      </c>
+          <t>This value set consists of the single code "sdoh". It is the minimum value set of category codes used in the US Core Condition Problems and Health Concerns Profile that any conformant system **SHALL** support to help identify the type of USCDI Health Status/Assessment data class being reported.</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr">
         <is>
-          <t>SCT,LOINC,hl7.terminology.r4</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="J199" t="inlineStr"/>
@@ -9744,12 +9732,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-screening-assessment-condition-category</t>
+          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-screening-assessment-observation-category</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>9.0.0-ballot</t>
+          <t>9.0.0</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -9759,28 +9747,32 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.40.2.48.10</t>
+          <t>2.16.840.1.113883.4.642.40.2.48.11</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>USCoreScreeningAssessmentConditionCategory</t>
+          <t>USCoreScreeningAssessmentObservationCategory</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>US Core Screening Assessment Condition Category</t>
+          <t>US Core Screening Assessment Observation Category</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>This value set consists of the single code "sdoh". It is the minimum value set of category codes used in the US Core Condition Problems and Health Concerns Profile that any conformant system **SHALL** support to help identify the type of USCDI Health Status/Assessment data class being reported.</t>
-        </is>
-      </c>
-      <c r="H200" t="inlineStr"/>
+          <t>This value set is the minimum value set of category codes used in the US Core Observation Screening Assessment and Simple Observation Profiles that any conformant system **SHALL** support to help identify the type of USCDI Health Status/Assessment data class being reported.</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>StructureDefinition/us-core-condition-problems-health-concerns,StructureDefinition/us-core-observation-screening-assessment</t>
+        </is>
+      </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Internal,THO</t>
         </is>
       </c>
       <c r="J200" t="inlineStr"/>
@@ -9788,12 +9780,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-screening-assessment-observation-category</t>
+          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-screening-assessment-observation-maximum-category</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>9.0.0-ballot</t>
+          <t>9.0.0</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -9803,27 +9795,27 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.40.2.48.11</t>
+          <t>2.16.840.1.113883.4.642.40.2.48.12</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>USCoreScreeningAssessmentObservationCategory</t>
+          <t>USCoreScreeningAssessmentObservationMaximumCategory</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>US Core Screening Assessment Observation Category</t>
+          <t>US Core Screening Assessment Observation Maximum Category</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>This value set is the minimum value set of category codes used in the US Core Observation Screening Assessment and Simple Observation Profiles that any conformant system **SHALL** support to help identify the type of USCDI Health Status/Assessment data class being reported.</t>
+          <t>This value set is a value set of category codes used in the US Core Observation Screening Assessment that any conformant system **SHOULD** support to help identify the type of USCDI Health Status/Assessment data class being reported.</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-condition-problems-health-concerns,StructureDefinition/us-core-observation-screening-assessment</t>
+          <t>StructureDefinition/us-core-observation-screening-assessment</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -9836,12 +9828,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-screening-assessment-observation-maximum-category</t>
+          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-servicerequest-category</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>9.0.0-ballot</t>
+          <t>9.0.0</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -9851,32 +9843,32 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.40.2.48.12</t>
+          <t>2.16.840.1.113883.4.642.40.2.48.20</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>USCoreScreeningAssessmentObservationMaximumCategory</t>
+          <t>USCoreServiceRequestCategoryCodes</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>US Core Screening Assessment Observation Maximum Category</t>
+          <t>US Core ServiceRequest Category Codes</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>This value set is a value set of category codes used in the US Core Observation Screening Assessment that any conformant system **SHOULD** support to help identify the type of USCDI Health Status/Assessment data class being reported.</t>
+          <t>A set of SNOMED CT and LOINC concepts to classify a requested service</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-observation-screening-assessment</t>
+          <t>StructureDefinition/us-core-servicerequest</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>Internal,THO</t>
+          <t>SCT,Internal</t>
         </is>
       </c>
       <c r="J202" t="inlineStr"/>
@@ -9884,12 +9876,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-servicerequest-category</t>
+          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-simple-observation-category</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>9.0.0-ballot</t>
+          <t>9.0.0</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -9899,32 +9891,32 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.40.2.48.20</t>
+          <t>2.16.840.1.113883.4.642.40.2.48.13</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>USCoreServiceRequestCategoryCodes</t>
+          <t>USCoreSimpleObservationCategory</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>US Core ServiceRequest Category Codes</t>
+          <t>US Core Simple Observation Category</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>A set of SNOMED CT and LOINC concepts to classify a requested service</t>
+          <t>This value set is a value set of category codes used in the US Core Simple Observation and Condition Problems and Health Concerns Profiles that any conformant system **SHOULD** support to help identify the type of USCDI Health Status/Assessment data class being reported.</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-servicerequest</t>
+          <t>StructureDefinition/us-core-condition-problems-health-concerns,StructureDefinition/us-core-care-experience-preference,StructureDefinition/us-core-treatment-intervention-preference,StructureDefinition/us-core-observation-adi-documentation,StructureDefinition/us-core-simple-observation</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>SCT,Internal</t>
+          <t>Internal,THO</t>
         </is>
       </c>
       <c r="J203" t="inlineStr"/>
@@ -9932,12 +9924,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-simple-observation-category</t>
+          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-specimen-condition</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>9.0.0-ballot</t>
+          <t>9.0.0</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -9947,84 +9939,78 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.40.2.48.13</t>
+          <t>2.16.840.1.113883.4.642.40.2.48.14</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>USCoreSimpleObservationCategory</t>
+          <t>USCoreSpecimenCondition</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>US Core Simple Observation Category</t>
+          <t>US Core Specimen Condition</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>This value set is a value set of category codes used in the US Core Simple Observation and Condition Problems and Health Concerns Profiles that any conformant system **SHOULD** support to help identify the type of USCDI Health Status/Assessment data class being reported.</t>
+          <t>This value set contains concepts the provide information regarding a specimen, including the container, that does not meet a laboratory’s criteria for acceptability.</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-condition-problems-health-concerns,StructureDefinition/us-core-care-experience-preference,StructureDefinition/us-core-treatment-intervention-preference,StructureDefinition/us-core-observation-adi-documentation,StructureDefinition/us-core-simple-observation</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>Internal,THO</t>
-        </is>
-      </c>
+          <t>StructureDefinition/us-core-specimen</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-specimen-condition</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>9.0.0-ballot</t>
-        </is>
+          <t>http://phinvads.cdc.gov/fhir/ValueSet/2.16.840.1.114222.4.11.7900</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>1</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>2.16.840.1.113883.4.642.40.2.48.14</t>
-        </is>
-      </c>
+      <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr">
         <is>
-          <t>USCoreSpecimenCondition</t>
+          <t>PHVS_Industry_NAICS_Detail _ODH</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>US Core Specimen Condition</t>
+          <t>Industry NAICS Detail (ODH)</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>This value set contains concepts the provide information regarding a specimen, including the container, that does not meet a laboratory’s criteria for acceptability.</t>
+          <t>The Industry NAICS Detail (ODH) value set is to be used to capture self-reported industry within electronic health information systems to support direct patient care, population health and public health activities.  Industry is described as the economic or business sector of a business or enterprise.  For more information, a mapping to 2012 Census Industry Codes, and tips on using this value set go to the Occupational Data for Health (ODH) Hot Topics section on the PHIN VADS home page.</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-specimen</t>
-        </is>
-      </c>
-      <c r="I205" t="inlineStr"/>
+          <t>StructureDefinition/us-core-observation-occupation</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>THO</t>
+        </is>
+      </c>
       <c r="J205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>http://phinvads.cdc.gov/fhir/ValueSet/2.16.840.1.114222.4.11.7900</t>
+          <t>http://phinvads.cdc.gov/fhir/ValueSet/2.16.840.1.114222.4.11.7901</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -10038,17 +10024,17 @@
       <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr">
         <is>
-          <t>PHVS_Industry_NAICS_Detail _ODH</t>
+          <t>PHVS_Occupation_ONETSOC_Detail_ODH</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Industry NAICS Detail (ODH)</t>
+          <t>Occupation ONETSOC Detail (ODH)</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>The Industry NAICS Detail (ODH) value set is to be used to capture self-reported industry within electronic health information systems to support direct patient care, population health and public health activities.  Industry is described as the economic or business sector of a business or enterprise.  For more information, a mapping to 2012 Census Industry Codes, and tips on using this value set go to the Occupational Data for Health (ODH) Hot Topics section on the PHIN VADS home page.</t>
+          <t>The Occupation ONETSOC Detail (ODH) value set is to be used to capture self-reported occupation within electronic health information systems to support direct patient care, population health and public health activities.  Occupation is the type of work done by the subject.  It is based on the 2010 O*Net-SOC Classification System.  For more information, a mapping to 2010 Census Codes, and tips on using this value set go to the Occupational Data for Health (ODH) Hot Topics section on the PHIN VADS home page.</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -10066,11 +10052,13 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>http://phinvads.cdc.gov/fhir/ValueSet/2.16.840.1.114222.4.11.7901</t>
-        </is>
-      </c>
-      <c r="B207" t="n">
-        <v>1</v>
+          <t>http://terminology.hl7.org/ValueSet/CMSPlaceOfServiceCodes</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>1.0.0</t>
+        </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -10080,27 +10068,27 @@
       <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr">
         <is>
-          <t>PHVS_Occupation_ONETSOC_Detail_ODH</t>
+          <t>CMSPlaceOfServiceCodes</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Occupation ONETSOC Detail (ODH)</t>
+          <t>CMS Place of Service Codes (POS)</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>The Occupation ONETSOC Detail (ODH) value set is to be used to capture self-reported occupation within electronic health information systems to support direct patient care, population health and public health activities.  Occupation is the type of work done by the subject.  It is based on the 2010 O*Net-SOC Classification System.  For more information, a mapping to 2010 Census Codes, and tips on using this value set go to the Occupational Data for Health (ODH) Hot Topics section on the PHIN VADS home page.</t>
+          <t>This is the all codes value set for the CMS POS code system.</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-observation-occupation</t>
+          <t>StructureDefinition/us-core-location</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>THO</t>
+          <t>hl7.terminology.r4</t>
         </is>
       </c>
       <c r="J207" t="inlineStr"/>
@@ -10108,7 +10096,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>http://terminology.hl7.org/ValueSet/CMSPlaceOfServiceCodes</t>
+          <t>http://terminology.hl7.org/ValueSet/Languages</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -10124,27 +10112,27 @@
       <c r="D208" t="inlineStr"/>
       <c r="E208" t="inlineStr">
         <is>
-          <t>CMSPlaceOfServiceCodes</t>
+          <t>Languages</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>CMS Place of Service Codes (POS)</t>
+          <t>Languages</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>This is the all codes value set for the CMS POS code system.</t>
+          <t>This value set defines a set of codes for the representation of the names of languages. It uses the list of ISO 639-2 concepts using the ISO 639-1 2-digit code for a concept where possible and the 3-digit terminological code where there is no  2-digit code.</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-location</t>
+          <t>StructureDefinition/us-core-patient</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>hl7.terminology.r4</t>
+          <t>hl7.fhir.uv.xver-r5.r4</t>
         </is>
       </c>
       <c r="J208" t="inlineStr"/>
@@ -10152,7 +10140,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>http://terminology.hl7.org/ValueSet/Languages</t>
+          <t>http://terminology.hl7.org/ValueSet/USPS-State</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -10168,27 +10156,27 @@
       <c r="D209" t="inlineStr"/>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Languages</t>
+          <t>UspsTwoLetterAlphabeticCodes</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Languages</t>
+          <t>USPS Two Letter Alphabetic Codes</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>This value set defines a set of codes for the representation of the names of languages. It uses the list of ISO 639-2 concepts using the ISO 639-1 2-digit code for a concept where possible and the 3-digit terminological code where there is no  2-digit code.</t>
+          <t>This value set defines two letter USPS alphabetic codes.</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-patient</t>
+          <t>StructureDefinition/us-core-practitioner,StructureDefinition/us-core-patient,StructureDefinition/us-core-location,StructureDefinition/us-core-jurisdiction,StructureDefinition/us-core-organization</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>hl7.fhir.uv.xver-r5.r4</t>
+          <t>hl7.terminology.r4</t>
         </is>
       </c>
       <c r="J209" t="inlineStr"/>
@@ -10196,12 +10184,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>http://terminology.hl7.org/ValueSet/USPS-State</t>
+          <t>http://terminology.hl7.org/ValueSet/provenance-agent-type</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>1.0.0</t>
+          <t>1.0.1</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -10209,30 +10197,34 @@
           <t>active</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>2.16.840.1.113883.4.642.3.1003</t>
+        </is>
+      </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>UspsTwoLetterAlphabeticCodes</t>
+          <t>ProvenanceParticipantType</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>USPS Two Letter Alphabetic Codes</t>
+          <t>Provenance participant type</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>This value set defines two letter USPS alphabetic codes.</t>
+          <t>The type of participation a provenance participant.</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-practitioner,StructureDefinition/us-core-patient,StructureDefinition/us-core-location,StructureDefinition/us-core-jurisdiction,StructureDefinition/us-core-organization</t>
+          <t>StructureDefinition/us-core-provenance</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>hl7.terminology.r4</t>
+          <t>THO</t>
         </is>
       </c>
       <c r="J210" t="inlineStr"/>
@@ -10240,12 +10232,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>http://terminology.hl7.org/ValueSet/provenance-agent-type</t>
+          <t>http://terminology.hl7.org/ValueSet/v2-0092</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>1.0.1</t>
+          <t>2.0.0</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -10255,32 +10247,32 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.3.1003</t>
+          <t>2.16.840.1.113883.21.40</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>ProvenanceParticipantType</t>
+          <t>Hl7VSReAdmissionIndicator</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Provenance participant type</t>
+          <t>hl7VS-re-admissionIndicator</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>The type of participation a provenance participant.</t>
+          <t>Value Set of codes which are used to specify that a patient is being re-admitted to a healthcare facility from which they were discharged, and indicates the circumstances around such re-admission.</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-provenance</t>
+          <t>StructureDefinition/us-core-encounter</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>THO</t>
+          <t>THO (V2)</t>
         </is>
       </c>
       <c r="J211" t="inlineStr"/>
@@ -10288,7 +10280,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>http://terminology.hl7.org/ValueSet/v2-0092</t>
+          <t>http://terminology.hl7.org/ValueSet/v2-0116</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -10303,27 +10295,27 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.21.40</t>
+          <t>2.16.840.1.113883.21.51</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Hl7VSReAdmissionIndicator</t>
+          <t>Hl7VSBedStatus</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>hl7VS-re-admissionIndicator</t>
+          <t>hl7VS-bedStatus</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Value Set of codes which are used to specify that a patient is being re-admitted to a healthcare facility from which they were discharged, and indicates the circumstances around such re-admission.</t>
+          <t>Value Set of codes that specify the state of a bed in an inpatient setting, and is used to determine if a patient may be assigned to it or not.</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-encounter</t>
+          <t>StructureDefinition/us-core-location</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -10336,7 +10328,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>http://terminology.hl7.org/ValueSet/v2-0116</t>
+          <t>http://terminology.hl7.org/ValueSet/v2-0371</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -10351,27 +10343,27 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.21.51</t>
+          <t>2.16.840.1.113883.21.245</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Hl7VSBedStatus</t>
+          <t>Hl7VSAdditivePreservative</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>hl7VS-bedStatus</t>
+          <t>hl7VS-additivePreservative</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Value Set of codes that specify the state of a bed in an inpatient setting, and is used to determine if a patient may be assigned to it or not.</t>
+          <t>Concepts specifying any additive introduced to the specimen before or at the time of collection.  These additives may be introduced in order to preserve, maintain or enhance the particular nature or component of the specimen.  Used in Version 2 messaging in the SPM segment.</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-location</t>
+          <t>StructureDefinition/us-core-specimen</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -10384,7 +10376,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>http://terminology.hl7.org/ValueSet/v2-0371</t>
+          <t>http://terminology.hl7.org/ValueSet/v2-0493</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -10399,27 +10391,27 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.21.245</t>
+          <t>2.16.840.1.113883.21.333</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Hl7VSAdditivePreservative</t>
+          <t>Hl7VSSpecimenCondition</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>hl7VS-additivePreservative</t>
+          <t>hl7VS-specimenCondition</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Concepts specifying any additive introduced to the specimen before or at the time of collection.  These additives may be introduced in order to preserve, maintain or enhance the particular nature or component of the specimen.  Used in Version 2 messaging in the SPM segment.</t>
+          <t>Concepts of modes or states of being that describe the nature of a specimen.  Used in Version 2 messaging in the SPM segment.</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-specimen</t>
+          <t>ValueSet/us-core-specimen-condition</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -10432,7 +10424,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>http://terminology.hl7.org/ValueSet/v2-0493</t>
+          <t>http://terminology.hl7.org/ValueSet/v2-0916</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -10447,27 +10439,27 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.21.333</t>
+          <t>2.16.840.1.113883.21.440</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Hl7VSSpecimenCondition</t>
+          <t>Hl7VSRelevantClincialInformation</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>hl7VS-specimenCondition</t>
+          <t>hl7VS-relevantClincialInformation</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Concepts of modes or states of being that describe the nature of a specimen.  Used in Version 2 messaging in the SPM segment.</t>
+          <t>Value Set of codes that specify additional clinical information about the patient or specimen to report the supporting and/or suspected diagnosis and clinical findings on requests for interpreted diagnostic studies.</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>ValueSet/us-core-specimen-condition</t>
+          <t>StructureDefinition/us-core-specimen</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -10480,12 +10472,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>http://terminology.hl7.org/ValueSet/v2-0916</t>
+          <t>http://terminology.hl7.org/ValueSet/v2-2.7-0360</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2.0.0</t>
+          <t>0360</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -10493,47 +10485,47 @@
           <t>active</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>2.16.840.1.113883.21.440</t>
-        </is>
-      </c>
+      <c r="D216" t="inlineStr"/>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Hl7VSRelevantClincialInformation</t>
+          <t>v2.0360.2.7</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>hl7VS-relevantClincialInformation</t>
+          <t>v2 table 0360</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Value Set of codes that specify additional clinical information about the patient or specimen to report the supporting and/or suspected diagnosis and clinical findings on requests for interpreted diagnostic studies.</t>
+          <t xml:space="preserve"> Version 2.7</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-specimen</t>
+          <t>FHIR Value set/code system definition for HL7 v2 table 0360 ver 2.9 ( Degree/License/Certificate)</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
+          <t>StructureDefinition/us-core-practitioner</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
           <t>THO (V2)</t>
         </is>
       </c>
-      <c r="J216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>http://terminology.hl7.org/ValueSet/v2-2.7-0360</t>
+          <t>http://terminology.hl7.org/ValueSet/v3-ActCode</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>0360</t>
+          <t>3.0.0</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -10544,39 +10536,35 @@
       <c r="D217" t="inlineStr"/>
       <c r="E217" t="inlineStr">
         <is>
-          <t>v2.0360.2.7</t>
+          <t>ActCode</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>v2 table 0360</t>
+          <t>v3 Code System ActCode</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Version 2.7</t>
+          <t>A code specifying the particular kind of Act that the Act-instance represents within its class.  Constraints:  The kind of Act (e.g. physical examination, serum potassium, inpatient encounter, charge financial transaction, etc.) is specified with a code from one of several, typically external, coding systems.  The coding system will depend on the class of Act, such as LOINC for observations, etc. Conceptually, the Act.code must be a specialization of the Act.classCode. This is why the structure of ActClass domain should be reflected in the superstructure of the ActCode domain and then individual codes or externally referenced vocabularies subordinated under these domains that reflect the ActClass structure. Act.classCode and Act.code are not modifiers of each other but the Act.code concept should really imply the Act.classCode concept. For a negative example, it is not appropriate to use an Act.code "potassium" together with and Act.classCode for "laboratory observation" to somehow mean "potassium laboratory observation" and then use the same Act.code for "potassium" together with Act.classCode for "medication" to mean "substitution of potassium". This mutually modifying use of Act.code and Act.classCode is not permitted.</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>FHIR Value set/code system definition for HL7 v2 table 0360 ver 2.9 ( Degree/License/Certificate)</t>
+          <t>StructureDefinition/us-core-adi-documentreference,StructureDefinition/us-core-documentreference</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-practitioner</t>
-        </is>
-      </c>
-      <c r="J217" t="inlineStr">
-        <is>
-          <t>THO (V2)</t>
-        </is>
-      </c>
+          <t>THO (V3)</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>http://terminology.hl7.org/ValueSet/v3-ActCode</t>
+          <t>http://terminology.hl7.org/ValueSet/v3-ActEncounterCode</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -10589,25 +10577,29 @@
           <t>active</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>2.16.840.1.113883.1.11.13955</t>
+        </is>
+      </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>ActCode</t>
+          <t>ActEncounterCode</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>v3 Code System ActCode</t>
+          <t>ActEncounterCode</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>A code specifying the particular kind of Act that the Act-instance represents within its class.  Constraints:  The kind of Act (e.g. physical examination, serum potassium, inpatient encounter, charge financial transaction, etc.) is specified with a code from one of several, typically external, coding systems.  The coding system will depend on the class of Act, such as LOINC for observations, etc. Conceptually, the Act.code must be a specialization of the Act.classCode. This is why the structure of ActClass domain should be reflected in the superstructure of the ActCode domain and then individual codes or externally referenced vocabularies subordinated under these domains that reflect the ActClass structure. Act.classCode and Act.code are not modifiers of each other but the Act.code concept should really imply the Act.classCode concept. For a negative example, it is not appropriate to use an Act.code "potassium" together with and Act.classCode for "laboratory observation" to somehow mean "potassium laboratory observation" and then use the same Act.code for "potassium" together with Act.classCode for "medication" to mean "substitution of potassium". This mutually modifying use of Act.code and Act.classCode is not permitted.</t>
+          <t>Domain provides codes that qualify the ActEncounterClass (ENC)</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-adi-documentreference,StructureDefinition/us-core-documentreference</t>
+          <t>StructureDefinition/us-core-encounter</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -10620,7 +10612,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>http://terminology.hl7.org/ValueSet/v3-ActEncounterCode</t>
+          <t>http://terminology.hl7.org/ValueSet/v3-ActPharmacySupplyType</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -10635,27 +10627,27 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.1.11.13955</t>
+          <t>2.16.840.1.113883.1.11.16208</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>ActEncounterCode</t>
+          <t>ActPharmacySupplyType</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>ActEncounterCode</t>
+          <t>ActPharmacySupplyType</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Domain provides codes that qualify the ActEncounterClass (ENC)</t>
+          <t>Identifies types of dispensing events</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-encounter</t>
+          <t>StructureDefinition/us-core-medicationdispense</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -10668,7 +10660,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>http://terminology.hl7.org/ValueSet/v3-ActPharmacySupplyType</t>
+          <t>http://terminology.hl7.org/ValueSet/v3-ActPriority</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -10683,27 +10675,27 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.1.11.16208</t>
+          <t>2.16.840.1.113883.1.11.16866</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>ActPharmacySupplyType</t>
+          <t>ActPriority</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>ActPharmacySupplyType</t>
+          <t>ActPriority</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Identifies types of dispensing events</t>
+          <t>A code or set of codes (e.g., for routine, emergency,) specifying the urgency under which the Act happened, can happen, is happening, is intended to happen, or is requested/demanded to happen.    *Discussion:* This attribute is used in orders to indicate the ordered priority, and in event documentation it indicates the actual priority used to perform the act. In definition mood it indicates the available priorities.</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-medicationdispense</t>
+          <t>StructureDefinition/us-core-encounter</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -10716,7 +10708,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>http://terminology.hl7.org/ValueSet/v3-ActPriority</t>
+          <t>http://terminology.hl7.org/ValueSet/v3-ActSubstanceAdminSubstitutionCode</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -10731,27 +10723,27 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.1.11.16866</t>
+          <t>2.16.840.1.113883.1.11.16621</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>ActPriority</t>
+          <t>ActSubstanceAdminSubstitutionCode</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>ActPriority</t>
+          <t>ActSubstanceAdminSubstitutionCode</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>A code or set of codes (e.g., for routine, emergency,) specifying the urgency under which the Act happened, can happen, is happening, is intended to happen, or is requested/demanded to happen.    *Discussion:* This attribute is used in orders to indicate the ordered priority, and in event documentation it indicates the actual priority used to perform the act. In definition mood it indicates the available priorities.</t>
+          <t>***No description***</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-encounter</t>
+          <t>StructureDefinition/us-core-medicationrequest,StructureDefinition/us-core-medicationdispense</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -10764,12 +10756,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>http://terminology.hl7.org/ValueSet/v3-ActSubstanceAdminSubstitutionCode</t>
+          <t>http://terminology.hl7.org/ValueSet/v3-HL7FormatCodes</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>3.0.0</t>
+          <t>2.1.0</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -10779,32 +10771,32 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.1.11.16621</t>
+          <t>2.16.840.1.113883.11.19752</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>ActSubstanceAdminSubstitutionCode</t>
+          <t>HL7FormatCodes</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>ActSubstanceAdminSubstitutionCode</t>
+          <t>HL7 ValueSet of Format Codes for use with Document Sharing</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>***No description***</t>
+          <t>The HL7-FormatCodes value set is defined to be the set of FormatCode(s) defined by implementation guides published by HL7 and other SDOs. The use of a formatCode from the FormatCodes value set specifies the technical format that a document conforms to. The formatCode is a further specialization more detailed than the mime-type. The formatCode provides sufficient information to allow any potential document content consumer to know if it can process and/or display the content of the document based on the document encoding, structure and template conformance indicated by the formatCode. The set of formatCodes is intended to be extensible. The Content Logical Description is defined intentionally to permit formatCodes defined by other Standards Development Organizations to be added by inclusion of additional formatCode Code Systems.</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-medicationrequest,StructureDefinition/us-core-medicationdispense</t>
+          <t>StructureDefinition/us-core-adi-documentreference,StructureDefinition/us-core-documentreference</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>THO (V3)</t>
+          <t>THO (V3),Other</t>
         </is>
       </c>
       <c r="J222" t="inlineStr"/>
@@ -10812,12 +10804,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>http://terminology.hl7.org/ValueSet/v3-HL7FormatCodes</t>
+          <t>http://terminology.hl7.org/ValueSet/v3-PurposeOfUse</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2.1.0</t>
+          <t>3.1.0</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -10827,32 +10819,32 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.11.19752</t>
+          <t>2.16.840.1.113883.1.11.20448</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>HL7FormatCodes</t>
+          <t>PurposeOfUse</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>HL7 ValueSet of Format Codes for use with Document Sharing</t>
+          <t>PurposeOfUse</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>The HL7-FormatCodes value set is defined to be the set of FormatCode(s) defined by implementation guides published by HL7 and other SDOs. The use of a formatCode from the FormatCodes value set specifies the technical format that a document conforms to. The formatCode is a further specialization more detailed than the mime-type. The formatCode provides sufficient information to allow any potential document content consumer to know if it can process and/or display the content of the document based on the document encoding, structure and template conformance indicated by the formatCode. The set of formatCodes is intended to be extensible. The Content Logical Description is defined intentionally to permit formatCodes defined by other Standards Development Organizations to be added by inclusion of additional formatCode Code Systems.</t>
+          <t>Supports communication of purpose of use at a general level.</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-adi-documentreference,StructureDefinition/us-core-documentreference</t>
+          <t>StructureDefinition/us-core-provenance</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>THO (V3),Other</t>
+          <t>THO (V3)</t>
         </is>
       </c>
       <c r="J223" t="inlineStr"/>
@@ -10860,12 +10852,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>http://terminology.hl7.org/ValueSet/v3-PurposeOfUse</t>
+          <t>http://terminology.hl7.org/ValueSet/v3-ServiceDeliveryLocationRoleType</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>3.1.0</t>
+          <t>3.0.0</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -10875,27 +10867,27 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.1.11.20448</t>
+          <t>2.16.840.1.113883.1.11.17660</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>PurposeOfUse</t>
+          <t>ServiceDeliveryLocationRoleType</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>PurposeOfUse</t>
+          <t>ServiceDeliveryLocationRoleType</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Supports communication of purpose of use at a general level.</t>
+          <t>A role of a place that further classifies the setting (e.g., accident site, road side, work site, community location) in which services are delivered.</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-provenance</t>
+          <t>StructureDefinition/us-core-location,StructureDefinition/us-core-servicerequest</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -10908,7 +10900,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>http://terminology.hl7.org/ValueSet/v3-ServiceDeliveryLocationRoleType</t>
+          <t>http://terminology.hl7.org/ValueSet/v3-SubstanceAdminSubstitutionReason</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -10923,27 +10915,27 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.1.11.17660</t>
+          <t>2.16.840.1.113883.1.11.19377</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>ServiceDeliveryLocationRoleType</t>
+          <t>SubstanceAdminSubstitutionReason</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>ServiceDeliveryLocationRoleType</t>
+          <t>SubstanceAdminSubstitutionReason</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>A role of a place that further classifies the setting (e.g., accident site, road side, work site, community location) in which services are delivered.</t>
+          <t>***No description***</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-pmo-servicerequest,StructureDefinition/us-core-location,StructureDefinition/us-core-servicerequest</t>
+          <t>StructureDefinition/us-core-medicationrequest,StructureDefinition/us-core-medicationdispense</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -10956,12 +10948,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>http://terminology.hl7.org/ValueSet/v3-SubstanceAdminSubstitutionReason</t>
+          <t>http://terminology.hl7.org/ValueSet/v3-TribalEntityUS</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>3.0.0</t>
+          <t>4.0.0</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -10971,27 +10963,27 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.1.11.19377</t>
+          <t>2.16.840.1.113883.1.11.11631</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>SubstanceAdminSubstitutionReason</t>
+          <t>TribalEntityUS</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>SubstanceAdminSubstitutionReason</t>
+          <t>TribalEntityUS</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>***No description***</t>
+          <t>INDIAN ENTITIES RECOGNIZED AND ELIGIBLE TO RECEIVE SERVICES FROM THE UNITED STATES BUREAU OF INDIAN AFFAIRS</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-medicationrequest,StructureDefinition/us-core-medicationdispense</t>
+          <t>StructureDefinition/us-core-tribal-affiliation</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -11004,12 +10996,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>http://terminology.hl7.org/ValueSet/v3-TribalEntityUS</t>
+          <t>http://terminology.hl7.org/ValueSet/v3-USEncounterDischargeDisposition</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>4.0.0</t>
+          <t>5.0.0</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -11019,32 +11011,32 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.1.11.11631</t>
+          <t>2.16.840.1.113883.1.11.19453</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>TribalEntityUS</t>
+          <t>USEncounterDischargeDisposition</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>TribalEntityUS</t>
+          <t>USEncounterDischargeDisposition</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>INDIAN ENTITIES RECOGNIZED AND ELIGIBLE TO RECEIVE SERVICES FROM THE UNITED STATES BUREAU OF INDIAN AFFAIRS</t>
+          <t>These codes cannot be displayed because of AHA's NUBC Patient Discharge Status Codes Intellectual Property (IP) restrictions. To access these codes, see the [National Uniform Billing Committee](http://www.nubc.org/), manual UB-04, UB form locator 17.</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-tribal-affiliation</t>
+          <t>StructureDefinition/us-core-encounter</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>THO (V3)</t>
+          <t>hl7.terminology.r4</t>
         </is>
       </c>
       <c r="J227" t="inlineStr"/>
@@ -11052,12 +11044,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>http://terminology.hl7.org/ValueSet/v3-USEncounterDischargeDisposition</t>
+          <t>http://terminology.hl7.org/ValueSet/v3-UnitsOfMeasureCaseSensitive</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>5.0.0</t>
+          <t>3.0.0</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -11067,83 +11059,35 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.1.11.19453</t>
+          <t>2.16.840.1.113883.1.11.12839</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>USEncounterDischargeDisposition</t>
+          <t>UnitsOfMeasureCaseSensitive</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>USEncounterDischargeDisposition</t>
+          <t>UnitsOfMeasureCaseSensitive</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>These codes cannot be displayed because of AHA's NUBC Patient Discharge Status Codes Intellectual Property (IP) restrictions. To access these codes, see the [National Uniform Billing Committee](http://www.nubc.org/), manual UB-04, UB form locator 17.</t>
+          <t>**Description:** All units of measure.</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-encounter</t>
+          <t>StructureDefinition/us-core-smokingstatus</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>hl7.terminology.r4</t>
+          <t>UCUM</t>
         </is>
       </c>
       <c r="J228" t="inlineStr"/>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>http://terminology.hl7.org/ValueSet/v3-UnitsOfMeasureCaseSensitive</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>3.0.0</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>2.16.840.1.113883.1.11.12839</t>
-        </is>
-      </c>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t>UnitsOfMeasureCaseSensitive</t>
-        </is>
-      </c>
-      <c r="F229" t="inlineStr">
-        <is>
-          <t>UnitsOfMeasureCaseSensitive</t>
-        </is>
-      </c>
-      <c r="G229" t="inlineStr">
-        <is>
-          <t>**Description:** All units of measure.</t>
-        </is>
-      </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>StructureDefinition/us-core-smokingstatus</t>
-        </is>
-      </c>
-      <c r="I229" t="inlineStr">
-        <is>
-          <t>UCUM</t>
-        </is>
-      </c>
-      <c r="J229" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/input/images/tables/valueset-ref-all-list.xlsx
+++ b/input/images/tables/valueset-ref-all-list.xlsx
@@ -840,11 +840,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113762.1.4.1186.8</t>
+          <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113762.1.4.1240.11</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>20240625</v>
+        <v>20231129</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -853,27 +853,23 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.16.840.1.113762.1.4.1186.8</t>
+          <t>2.16.840.1.113762.1.4.1240.11</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CommonSubstancesForAllergyAndIntoleranceDocumentationIncludingRefutations</t>
+          <t>SexualOrientationIncludingNullsAndDataAbsentReason</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Common substances for allergy and intolerance documentation including refutations</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>This set was initially developed in 2018. Annual updates to the value set definitions have retained inactivated codes and incorporated the suggested VSAC remaps. THERE WERE SOME MINOR CHANGES TO THE REFUTATIONS AND THE SCT CLASS SET IN 2021, BUT THERE HAVE BEEN NO SIGNIFICANT UPDATES TO REFLECT NEW DRUG CLASSES, NEW DRUG SUBSTANCES, NEW DIETARY SUBSTANCES, OR NEW ENVIRONMENTAL SUBSTANCES THAT MAY HAVE EMERGED SINCE 2018.</t>
-        </is>
-      </c>
+          <t>Sexual Orientation Including nulls and Data Absent Reason</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-allergyintolerance</t>
+          <t>StructureDefinition/us-core-observation-sexual-orientation</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -882,11 +878,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113762.1.4.1240.11</t>
+          <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113762.1.4.1240.12</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20231129</v>
+        <v>20240906</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -895,23 +891,23 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.16.840.1.113762.1.4.1240.11</t>
+          <t>2.16.840.1.113762.1.4.1240.12</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SexualOrientationIncludingNullsAndDataAbsentReason</t>
+          <t>PregnancyStatusObservation</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sexual Orientation Including nulls and Data Absent Reason</t>
+          <t>Pregnancy Status Observation</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-observation-sexual-orientation</t>
+          <t>StructureDefinition/us-core-observation-pregnancystatus</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -920,11 +916,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113762.1.4.1240.12</t>
+          <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113762.1.4.1240.3</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>20240906</v>
+        <v>20230628</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -933,23 +929,27 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2.16.840.1.113762.1.4.1240.12</t>
+          <t>2.16.840.1.113762.1.4.1240.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PregnancyStatusObservation</t>
+          <t>Sex</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pregnancy Status Observation</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+          <t>Sex</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Created specifically to support United States USCDI v3 data element "Sex"</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-observation-pregnancystatus</t>
+          <t>StructureDefinition/us-core-sex</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -958,11 +958,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113762.1.4.1240.3</t>
+          <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113762.1.4.1240.8</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>20230628</v>
+        <v>20231025</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -971,27 +971,27 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2.16.840.1.113762.1.4.1240.3</t>
+          <t>2.16.840.1.113762.1.4.1240.8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sex</t>
+          <t>MedicationAdherence</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sex</t>
+          <t>Medication Adherence</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Created specifically to support United States USCDI v3 data element "Sex"</t>
+          <t>This value set may change until publication of USCDI V4 representation in US Core and C-CDA is published in 2024</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-sex</t>
+          <t>StructureDefinition/us-core-medication-adherence</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1000,11 +1000,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113762.1.4.1240.8</t>
+          <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113762.1.4.1267.11</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>20231025</v>
+        <v>20240329</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1013,24 +1013,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2.16.840.1.113762.1.4.1240.8</t>
+          <t>2.16.840.1.113762.1.4.1267.11</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MedicationAdherence</t>
+          <t>InformationSourceForMedicationAdherence</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Medication Adherence</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>This value set may change until publication of USCDI V4 representation in US Core and C-CDA is published in 2024</t>
-        </is>
-      </c>
+          <t>Information Source for Medication Adherence</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>StructureDefinition/us-core-medication-adherence</t>
@@ -1042,11 +1038,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113762.1.4.1247.71</t>
+          <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113762.1.4.1267.13</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>20250702</v>
+        <v>20250610</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1055,36 +1051,44 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2.16.840.1.113762.1.4.1247.71</t>
+          <t>2.16.840.1.113762.1.4.1267.13</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SocialDeterminantsOfHealthGoals</t>
+          <t>ScreeningAndAssessmentSurveyCodes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Social Determinants of Health Goals</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>Screening and Assessment Survey Codes</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>All LOINC survey codes</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-goal</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>StructureDefinition/us-core-observation-screening-assessment</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>LOINC</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113762.1.4.1267.11</t>
+          <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113762.1.4.1267.16</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>20240329</v>
+        <v>20241005</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1093,23 +1097,23 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2.16.840.1.113762.1.4.1267.11</t>
+          <t>2.16.840.1.113762.1.4.1267.16</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>InformationSourceForMedicationAdherence</t>
+          <t>AnswerSetWithYesNoAndUnknowns</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Information Source for Medication Adherence</t>
+          <t>Answer Set with Yes No and Unknowns</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-medication-adherence</t>
+          <t>StructureDefinition/us-core-interpreter-needed,StructureDefinition/us-core-observation-adi-documentation</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -1118,11 +1122,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113762.1.4.1267.13</t>
+          <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113762.1.4.1267.22</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>20250610</v>
+        <v>20241015</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1131,44 +1135,36 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2.16.840.1.113762.1.4.1267.13</t>
+          <t>2.16.840.1.113762.1.4.1267.22</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ScreeningAndAssessmentSurveyCodes</t>
+          <t>RouteOfAdministrationOfTherapeuticAgents</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Screening and Assessment Survey Codes</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>All LOINC survey codes</t>
-        </is>
-      </c>
+          <t>Route of Administration of Therapeutic Agents</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-observation-screening-assessment</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>LOINC</t>
-        </is>
-      </c>
+          <t>StructureDefinition/us-core-medicationrequest,StructureDefinition/us-core-medicationdispense</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113762.1.4.1267.16</t>
+          <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113762.1.4.1267.23</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>20241005</v>
+        <v>20250510</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1177,23 +1173,23 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2.16.840.1.113762.1.4.1267.16</t>
+          <t>2.16.840.1.113762.1.4.1267.23</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AnswerSetWithYesNoAndUnknowns</t>
+          <t>EncounterType</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Answer Set with Yes No and Unknowns</t>
+          <t>Encounter Type</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-interpreter-needed,StructureDefinition/us-core-observation-adi-documentation</t>
+          <t>StructureDefinition/us-core-encounter</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -1202,11 +1198,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113762.1.4.1267.22</t>
+          <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113762.1.4.1267.24</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>20241015</v>
+        <v>20250529</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1215,36 +1211,44 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.16.840.1.113762.1.4.1267.22</t>
+          <t>2.16.840.1.113762.1.4.1267.24</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RouteOfAdministrationOfTherapeuticAgents</t>
+          <t>SpecimenConditionSCT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Route of Administration of Therapeutic Agents</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
+          <t>Specimen Condition SCT</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>This Specimen Condition SCT value set is an enumerated list created by the HL7 Orders and Observation WG’s lab subgroup to complement, without overlapping, the HL7 Specimen Condition value set (http://terminology.hl7.org/ValueSet/v2-0493). It is designed for use with the FHIR R4 Specimen Resource (https://hl7.org/fhir/R4/specimen.html), which has an extensible binding to the HL7 Specimen Condition value set. It can be used elsewhere and will be used in C-CDA.</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-medicationrequest,StructureDefinition/us-core-medicationdispense</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>ValueSet/us-core-specimen-condition</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>SCT</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113762.1.4.1267.23</t>
+          <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113762.1.4.1267.25</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>20250510</v>
+        <v>20250419</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1253,23 +1257,27 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2.16.840.1.113762.1.4.1267.23</t>
+          <t>2.16.840.1.113762.1.4.1267.25</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>EncounterType</t>
+          <t>DetailedRaceIncludingAbsenceReasons</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Encounter Type</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+          <t>Detailed race including absence reasons.</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>This value set is based on the US Core Detailed Race value set defined in US Core version 7.0 and earlier (https://hl7.org/fhir/us/core/STU7/ValueSet-detailed-race.html). A new OID has been assigned due to a slight change in scope: it includes the CDCREC code 2131-1 (Other Race) in place of the HL7 nullFlavor code "OTH" (Other). This version is intended to serve as the authoritative source for detailed race data going forward.</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-encounter</t>
+          <t>StructureDefinition/us-core-race</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -1278,11 +1286,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113762.1.4.1267.24</t>
+          <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113762.1.4.1267.3</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>20250529</v>
+        <v>20240217</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1291,27 +1299,23 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2.16.840.1.113762.1.4.1267.24</t>
+          <t>2.16.840.1.113762.1.4.1267.3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SpecimenConditionSCT</t>
+          <t>SmokingStatusComprehensive</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Specimen Condition SCT</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>This Specimen Condition SCT value set is an enumerated list created by the HL7 Orders and Observation WG’s lab subgroup to complement, without overlapping, the HL7 Specimen Condition value set (http://terminology.hl7.org/ValueSet/v2-0493). It is designed for use with the FHIR R4 Specimen Resource (https://hl7.org/fhir/R4/specimen.html), which has an extensible binding to the HL7 Specimen Condition value set. It can be used elsewhere and will be used in C-CDA.</t>
-        </is>
-      </c>
+          <t>Smoking status comprehensive</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>ValueSet/us-core-specimen-condition</t>
+          <t>StructureDefinition/us-core-smokingstatus</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1324,11 +1328,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113762.1.4.1267.25</t>
+          <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113762.1.4.1267.31</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>20250419</v>
+        <v>20250516</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1337,27 +1341,27 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2.16.840.1.113762.1.4.1267.25</t>
+          <t>2.16.840.1.113762.1.4.1267.31</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>DetailedRaceIncludingAbsenceReasons</t>
+          <t>HealthcareServiceLocationTypeCombined</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Detailed race including absence reasons.</t>
+          <t>Healthcare Service Location Type Combined</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>This value set is based on the US Core Detailed Race value set defined in US Core version 7.0 and earlier (https://hl7.org/fhir/us/core/STU7/ValueSet-detailed-race.html). A new OID has been assigned due to a slight change in scope: it includes the CDCREC code 2131-1 (Other Race) in place of the HL7 nullFlavor code "OTH" (Other). This version is intended to serve as the authoritative source for detailed race data going forward.</t>
+          <t>This value set consolidates encounter type codes from the two code systems permitted by USCDI for representing encounter location, as specified in USCDI v5.(https://www.healthit.gov/isp/taxonomy/term/1336/uscdi-v5)</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-race</t>
+          <t>ValueSet/us-core-location-type</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -1366,11 +1370,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113762.1.4.1267.3</t>
+          <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113762.1.4.1267.43</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>20240217</v>
+        <v>20260321</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1379,40 +1383,48 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2.16.840.1.113762.1.4.1267.3</t>
+          <t>2.16.840.1.113762.1.4.1267.43</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SmokingStatusComprehensive</t>
+          <t>AllergenConceptsMedicationsFoodsAndEnvironmentalSubstancesIncludingRefutations</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Smoking status comprehensive</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
+          <t>Allergen Concepts (Medications</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Foods</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-smokingstatus</t>
+          <t xml:space="preserve"> and Environmental Substances) including refutations.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>SCT</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
+          <t>The contained sets represent substances and products that may cause allergic reactions or intolerances, for use in documenting the responsible allergen across medication, dietary, and environmental categories in structured allergy record. It Includes concepts within from the following grouped value sets: RxNorm Allergen Concepts (Ingredient-Focused) (IN, MIN, PIN, BN) SNOMED CT Medicinal Product Allergens (by Structure) SNOMED CT Dietary Allergens (Food and Food Additives) SNOMED CT Environmental Allergens</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>StructureDefinition/us-core-allergyintolerance</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113762.1.4.1267.31</t>
+          <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113762.1.4.1267.6</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>20250516</v>
+        <v>20240222</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1421,27 +1433,23 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2.16.840.1.113762.1.4.1267.31</t>
+          <t>2.16.840.1.113762.1.4.1267.6</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>HealthcareServiceLocationTypeCombined</t>
+          <t>SmokingStatusType</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Healthcare Service Location Type Combined</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>This value set consolidates encounter type codes from the two code systems permitted by USCDI for representing encounter location, as specified in USCDI v5.(https://www.healthit.gov/isp/taxonomy/term/1336/uscdi-v5)</t>
-        </is>
-      </c>
+          <t>Smoking Status Type</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-location</t>
+          <t>StructureDefinition/us-core-smokingstatus</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -1450,11 +1458,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113762.1.4.1267.6</t>
+          <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113883.1.11.19579</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>20240222</v>
+        <v>20250724</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1463,36 +1471,40 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2.16.840.1.113762.1.4.1267.6</t>
+          <t>2.16.840.1.113883.1.11.19579</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>SmokingStatusType</t>
+          <t>FamilyMemberValue</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Smoking Status Type</t>
+          <t>Family Member Value</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-smokingstatus</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>StructureDefinition/us-core-familymemberhistory</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>THO (V3)</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113883.1.11.19579</t>
+          <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113883.11.20.12.1</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>20250724</v>
+        <v>20251204</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1501,23 +1513,23 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.1.11.19579</t>
+          <t>2.16.840.1.113883.11.20.12.1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FamilyMemberValue</t>
+          <t>PersonalAndLegalRelationshipRoleType</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Family Member Value</t>
+          <t>Personal And Legal Relationship Role Type</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-familymemberhistory</t>
+          <t>StructureDefinition/us-core-relatedperson</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1576,7 +1588,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>20240322</v>
+        <v>20251202</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1601,7 +1613,7 @@
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>StructureDefinition/pediatric-bmi-for-age,StructureDefinition/us-core-pulse-oximetry,StructureDefinition/us-core-bmi,StructureDefinition/head-occipital-frontal-circumference-percentile,StructureDefinition/us-core-body-temperature,StructureDefinition/us-core-respiratory-rate,StructureDefinition/us-core-vital-signs,StructureDefinition/pediatric-weight-for-height,StructureDefinition/us-core-head-circumference,StructureDefinition/us-core-heart-rate,StructureDefinition/us-core-body-weight,StructureDefinition/us-core-body-height,StructureDefinition/us-core-blood-pressure</t>
+          <t>StructureDefinition/pediatric-bmi-for-age,StructureDefinition/us-core-pulse-oximetry,StructureDefinition/head-occipital-frontal-circumference-percentile,StructureDefinition/us-core-bmi,StructureDefinition/us-core-body-temperature,StructureDefinition/us-core-respiratory-rate,StructureDefinition/us-core-vital-signs,StructureDefinition/us-core-heart-rate,StructureDefinition/us-core-head-circumference,StructureDefinition/pediatric-weight-for-height,StructureDefinition/us-core-body-weight,StructureDefinition/us-core-body-height,StructureDefinition/us-core-blood-pressure</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1773,7 +1785,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-practitionerrole</t>
+          <t>ValueSet/us-core-practitionerrole-specialty</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1824,7 +1836,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>hl7.terminology.r4</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
@@ -2059,7 +2071,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-practitioner,StructureDefinition/us-core-patient,StructureDefinition/us-core-familymemberhistory,StructureDefinition/us-core-relatedperson</t>
+          <t>StructureDefinition/us-core-practitioner,StructureDefinition/us-core-patient,StructureDefinition/us-core-relatedperson,StructureDefinition/us-core-familymemberhistory</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2395,7 +2407,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-specimen,StructureDefinition/pediatric-bmi-for-age,StructureDefinition/us-core-pulse-oximetry,StructureDefinition/us-core-observation-pregnancyintent,StructureDefinition/us-core-procedure,StructureDefinition/head-occipital-frontal-circumference-percentile,StructureDefinition/us-core-observation-lab,StructureDefinition/us-core-bmi,StructureDefinition/us-core-vital-signs,StructureDefinition/us-core-servicerequest,StructureDefinition/us-core-simple-observation,StructureDefinition/us-core-head-circumference,StructureDefinition/us-core-heart-rate,StructureDefinition/us-core-body-height,StructureDefinition/us-core-smokingstatus,StructureDefinition/us-core-care-experience-preference,StructureDefinition/us-core-observation-clinical-result,StructureDefinition/us-core-observation-screening-assessment,StructureDefinition/us-core-respiratory-rate,StructureDefinition/us-core-body-temperature,StructureDefinition/us-core-condition-encounter-diagnosis,StructureDefinition/us-core-condition-problems-health-concerns,StructureDefinition/pediatric-weight-for-height,StructureDefinition/us-core-observation-pregnancystatus,StructureDefinition/us-core-body-weight,StructureDefinition/us-core-observation-occupation,StructureDefinition/us-core-average-blood-pressure,StructureDefinition/us-core-treatment-intervention-preference,StructureDefinition/us-core-observation-adi-documentation,StructureDefinition/us-core-observation-sexual-orientation,StructureDefinition/us-core-blood-pressure</t>
+          <t>StructureDefinition/us-core-specimen,StructureDefinition/pediatric-bmi-for-age,StructureDefinition/us-core-pulse-oximetry,StructureDefinition/us-core-observation-pregnancyintent,StructureDefinition/us-core-procedure,StructureDefinition/head-occipital-frontal-circumference-percentile,StructureDefinition/us-core-bmi,StructureDefinition/us-core-observation-lab,StructureDefinition/us-core-vital-signs,StructureDefinition/us-core-servicerequest,StructureDefinition/us-core-simple-observation,StructureDefinition/us-core-head-circumference,StructureDefinition/us-core-heart-rate,StructureDefinition/us-core-body-height,StructureDefinition/us-core-smokingstatus,StructureDefinition/us-core-care-experience-preference,StructureDefinition/us-core-observation-clinical-result,StructureDefinition/us-core-body-temperature,StructureDefinition/us-core-respiratory-rate,StructureDefinition/us-core-observation-screening-assessment,StructureDefinition/us-core-condition-encounter-diagnosis,StructureDefinition/us-core-condition-problems-health-concerns,StructureDefinition/pediatric-weight-for-height,StructureDefinition/us-core-observation-pregnancystatus,StructureDefinition/us-core-body-weight,StructureDefinition/us-core-observation-occupation,StructureDefinition/us-core-average-blood-pressure,StructureDefinition/us-core-treatment-intervention-preference,StructureDefinition/us-core-observation-adi-documentation,StructureDefinition/us-core-observation-sexual-orientation,StructureDefinition/us-core-blood-pressure</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2539,7 +2551,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-adi-documentreference,StructureDefinition/us-core-documentreference,StructureDefinition/us-core-practitionerrole</t>
+          <t>StructureDefinition/us-core-adi-documentreference,ValueSet/us-core-practitionerrole-specialty,StructureDefinition/us-core-documentreference</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3739,7 +3751,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>StructureDefinition/pediatric-bmi-for-age,StructureDefinition/us-core-pulse-oximetry,StructureDefinition/us-core-observation-pregnancyintent,StructureDefinition/head-occipital-frontal-circumference-percentile,StructureDefinition/us-core-observation-lab,StructureDefinition/us-core-bmi,StructureDefinition/us-core-vital-signs,StructureDefinition/us-core-simple-observation,StructureDefinition/us-core-head-circumference,StructureDefinition/us-core-heart-rate,StructureDefinition/us-core-body-height,StructureDefinition/us-core-smokingstatus,StructureDefinition/us-core-care-experience-preference,StructureDefinition/us-core-observation-clinical-result,StructureDefinition/us-core-observation-screening-assessment,StructureDefinition/us-core-respiratory-rate,StructureDefinition/us-core-body-temperature,StructureDefinition/pediatric-weight-for-height,StructureDefinition/us-core-observation-pregnancystatus,StructureDefinition/us-core-body-weight,StructureDefinition/us-core-observation-occupation,StructureDefinition/us-core-average-blood-pressure,StructureDefinition/us-core-treatment-intervention-preference,StructureDefinition/us-core-observation-adi-documentation,StructureDefinition/us-core-observation-sexual-orientation,StructureDefinition/us-core-blood-pressure</t>
+          <t>StructureDefinition/pediatric-bmi-for-age,StructureDefinition/us-core-pulse-oximetry,StructureDefinition/us-core-observation-pregnancyintent,StructureDefinition/head-occipital-frontal-circumference-percentile,StructureDefinition/us-core-bmi,StructureDefinition/us-core-observation-lab,StructureDefinition/us-core-vital-signs,StructureDefinition/us-core-simple-observation,StructureDefinition/us-core-head-circumference,StructureDefinition/us-core-heart-rate,StructureDefinition/us-core-body-height,StructureDefinition/us-core-smokingstatus,StructureDefinition/us-core-care-experience-preference,StructureDefinition/us-core-observation-clinical-result,StructureDefinition/us-core-body-temperature,StructureDefinition/us-core-respiratory-rate,StructureDefinition/us-core-observation-screening-assessment,StructureDefinition/pediatric-weight-for-height,StructureDefinition/us-core-observation-pregnancystatus,StructureDefinition/us-core-body-weight,StructureDefinition/us-core-observation-occupation,StructureDefinition/us-core-average-blood-pressure,StructureDefinition/us-core-treatment-intervention-preference,StructureDefinition/us-core-observation-adi-documentation,StructureDefinition/us-core-observation-sexual-orientation,StructureDefinition/us-core-blood-pressure</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5851,7 +5863,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-specimen,StructureDefinition/us-core-documentreference,StructureDefinition/us-core-observation-pregnancyintent,StructureDefinition/us-core-procedure,StructureDefinition/us-core-observation-lab,StructureDefinition/us-core-vital-signs,StructureDefinition/us-core-careplan,StructureDefinition/us-core-organization,StructureDefinition/us-core-adi-documentreference,StructureDefinition/us-core-head-circumference,StructureDefinition/us-core-heart-rate,StructureDefinition/us-core-practitioner,StructureDefinition/us-core-practitionerrole,StructureDefinition/us-core-body-height,StructureDefinition/us-core-smokingstatus,StructureDefinition/us-core-patient,StructureDefinition/us-core-provenance,StructureDefinition/us-core-observation-clinical-result,StructureDefinition/us-core-respiratory-rate,StructureDefinition/us-core-body-temperature,StructureDefinition/us-core-questionnaireresponse,StructureDefinition/us-core-condition-encounter-diagnosis,StructureDefinition/us-core-condition-problems-health-concerns,StructureDefinition/pediatric-weight-for-height,StructureDefinition/us-core-observation-pregnancystatus,StructureDefinition/us-core-medicationdispense,StructureDefinition/us-core-device,StructureDefinition/us-core-treatment-intervention-preference,StructureDefinition/pediatric-bmi-for-age,StructureDefinition/us-core-pulse-oximetry,StructureDefinition/us-core-diagnosticreport-lab,StructureDefinition/us-core-encounter,StructureDefinition/head-occipital-frontal-circumference-percentile,StructureDefinition/us-core-bmi,StructureDefinition/us-core-coverage,StructureDefinition/us-core-servicerequest,StructureDefinition/us-core-simple-observation,StructureDefinition/us-core-diagnosticreport-note,StructureDefinition/us-core-medicationrequest,StructureDefinition/us-core-medication,StructureDefinition/us-core-care-experience-preference,StructureDefinition/us-core-careteam,StructureDefinition/us-core-goal,StructureDefinition/us-core-observation-screening-assessment,StructureDefinition/us-core-immunization,StructureDefinition/us-core-familymemberhistory,StructureDefinition/us-core-relatedperson,StructureDefinition/us-core-body-weight,StructureDefinition/us-core-observation-occupation,StructureDefinition/us-core-average-blood-pressure,StructureDefinition/us-core-location,StructureDefinition/us-core-observation-adi-documentation,StructureDefinition/us-core-observation-sexual-orientation,StructureDefinition/us-core-allergyintolerance,StructureDefinition/us-core-blood-pressure</t>
+          <t>StructureDefinition/us-core-specimen,StructureDefinition/us-core-documentreference,StructureDefinition/us-core-observation-pregnancyintent,StructureDefinition/us-core-procedure,StructureDefinition/us-core-observation-lab,StructureDefinition/us-core-vital-signs,StructureDefinition/us-core-careplan,StructureDefinition/us-core-organization,StructureDefinition/us-core-adi-documentreference,StructureDefinition/us-core-head-circumference,StructureDefinition/us-core-heart-rate,StructureDefinition/us-core-practitioner,StructureDefinition/us-core-practitionerrole,StructureDefinition/us-core-body-height,StructureDefinition/us-core-smokingstatus,StructureDefinition/us-core-patient,StructureDefinition/us-core-observation-clinical-result,StructureDefinition/us-core-provenance,StructureDefinition/us-core-body-temperature,StructureDefinition/us-core-respiratory-rate,StructureDefinition/us-core-questionnaireresponse,StructureDefinition/us-core-condition-encounter-diagnosis,StructureDefinition/us-core-condition-problems-health-concerns,StructureDefinition/pediatric-weight-for-height,StructureDefinition/us-core-observation-pregnancystatus,StructureDefinition/us-core-medicationdispense,StructureDefinition/us-core-device,StructureDefinition/us-core-treatment-intervention-preference,StructureDefinition/pediatric-bmi-for-age,StructureDefinition/us-core-pulse-oximetry,StructureDefinition/us-core-diagnosticreport-lab,StructureDefinition/us-core-encounter,StructureDefinition/head-occipital-frontal-circumference-percentile,StructureDefinition/us-core-bmi,StructureDefinition/us-core-coverage,StructureDefinition/us-core-servicerequest,StructureDefinition/us-core-simple-observation,StructureDefinition/us-core-diagnosticreport-note,StructureDefinition/us-core-medicationrequest,StructureDefinition/us-core-medication,StructureDefinition/us-core-care-experience-preference,StructureDefinition/us-core-goal,StructureDefinition/us-core-careteam,StructureDefinition/us-core-observation-screening-assessment,StructureDefinition/us-core-immunization,StructureDefinition/us-core-relatedperson,StructureDefinition/us-core-familymemberhistory,StructureDefinition/us-core-body-weight,StructureDefinition/us-core-observation-occupation,StructureDefinition/us-core-average-blood-pressure,StructureDefinition/us-core-observation-sexual-orientation,StructureDefinition/us-core-observation-adi-documentation,StructureDefinition/us-core-location,StructureDefinition/us-core-allergyintolerance,StructureDefinition/us-core-blood-pressure</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -6907,7 +6919,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>StructureDefinition/pediatric-bmi-for-age,StructureDefinition/us-core-pulse-oximetry,StructureDefinition/us-core-observation-pregnancyintent,StructureDefinition/us-core-bmi,StructureDefinition/us-core-observation-clinical-result,StructureDefinition/head-occipital-frontal-circumference-percentile,StructureDefinition/us-core-observation-lab,StructureDefinition/us-core-observation-screening-assessment,StructureDefinition/us-core-body-temperature,StructureDefinition/us-core-respiratory-rate,StructureDefinition/us-core-vital-signs,StructureDefinition/pediatric-weight-for-height,StructureDefinition/us-core-head-circumference,StructureDefinition/us-core-heart-rate,StructureDefinition/us-core-observation-pregnancystatus,StructureDefinition/us-core-body-weight,StructureDefinition/us-core-observation-occupation,StructureDefinition/us-core-average-blood-pressure,StructureDefinition/us-core-body-height,StructureDefinition/us-core-smokingstatus,StructureDefinition/us-core-observation-sexual-orientation,StructureDefinition/us-core-blood-pressure</t>
+          <t>StructureDefinition/pediatric-bmi-for-age,StructureDefinition/us-core-pulse-oximetry,StructureDefinition/us-core-observation-pregnancyintent,StructureDefinition/us-core-observation-clinical-result,StructureDefinition/us-core-observation-lab,StructureDefinition/head-occipital-frontal-circumference-percentile,StructureDefinition/us-core-bmi,StructureDefinition/us-core-observation-screening-assessment,StructureDefinition/us-core-body-temperature,StructureDefinition/us-core-respiratory-rate,StructureDefinition/us-core-vital-signs,StructureDefinition/us-core-heart-rate,StructureDefinition/us-core-head-circumference,StructureDefinition/pediatric-weight-for-height,StructureDefinition/us-core-observation-pregnancystatus,StructureDefinition/us-core-body-weight,StructureDefinition/us-core-observation-occupation,StructureDefinition/us-core-average-blood-pressure,StructureDefinition/us-core-observation-sexual-orientation,StructureDefinition/us-core-body-height,StructureDefinition/us-core-smokingstatus,StructureDefinition/us-core-blood-pressure</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -6955,7 +6967,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-care-experience-preference,StructureDefinition/us-core-goal,StructureDefinition/us-core-observation-pregnancyintent,StructureDefinition/us-core-observation-clinical-result,StructureDefinition/us-core-observation-lab,StructureDefinition/us-core-observation-screening-assessment,StructureDefinition/us-core-simple-observation,StructureDefinition/us-core-observation-pregnancystatus,StructureDefinition/us-core-observation-occupation,StructureDefinition/us-core-average-blood-pressure,StructureDefinition/us-core-treatment-intervention-preference,StructureDefinition/us-core-smokingstatus,StructureDefinition/us-core-observation-adi-documentation,StructureDefinition/us-core-observation-sexual-orientation</t>
+          <t>StructureDefinition/us-core-care-experience-preference,StructureDefinition/us-core-goal,StructureDefinition/us-core-observation-pregnancyintent,StructureDefinition/us-core-observation-clinical-result,StructureDefinition/us-core-observation-lab,StructureDefinition/us-core-observation-screening-assessment,StructureDefinition/us-core-simple-observation,StructureDefinition/us-core-observation-pregnancystatus,StructureDefinition/us-core-observation-occupation,StructureDefinition/us-core-average-blood-pressure,StructureDefinition/us-core-treatment-intervention-preference,StructureDefinition/us-core-observation-sexual-orientation,StructureDefinition/us-core-observation-adi-documentation,StructureDefinition/us-core-smokingstatus</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -7003,7 +7015,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>StructureDefinition/pediatric-bmi-for-age,StructureDefinition/us-core-pulse-oximetry,StructureDefinition/us-core-observation-pregnancyintent,StructureDefinition/head-occipital-frontal-circumference-percentile,StructureDefinition/us-core-observation-lab,StructureDefinition/us-core-bmi,StructureDefinition/us-core-vital-signs,StructureDefinition/us-core-simple-observation,StructureDefinition/us-core-head-circumference,StructureDefinition/us-core-heart-rate,StructureDefinition/us-core-body-height,StructureDefinition/us-core-smokingstatus,StructureDefinition/us-core-care-experience-preference,StructureDefinition/us-core-observation-clinical-result,StructureDefinition/us-core-observation-screening-assessment,StructureDefinition/us-core-respiratory-rate,StructureDefinition/us-core-body-temperature,StructureDefinition/pediatric-weight-for-height,StructureDefinition/us-core-observation-pregnancystatus,StructureDefinition/us-core-body-weight,StructureDefinition/us-core-observation-occupation,StructureDefinition/us-core-average-blood-pressure,StructureDefinition/us-core-treatment-intervention-preference,StructureDefinition/us-core-observation-adi-documentation,StructureDefinition/us-core-observation-sexual-orientation,StructureDefinition/us-core-blood-pressure</t>
+          <t>StructureDefinition/pediatric-bmi-for-age,StructureDefinition/us-core-pulse-oximetry,StructureDefinition/us-core-observation-pregnancyintent,StructureDefinition/head-occipital-frontal-circumference-percentile,StructureDefinition/us-core-bmi,StructureDefinition/us-core-observation-lab,StructureDefinition/us-core-vital-signs,StructureDefinition/us-core-simple-observation,StructureDefinition/us-core-head-circumference,StructureDefinition/us-core-heart-rate,StructureDefinition/us-core-body-height,StructureDefinition/us-core-smokingstatus,StructureDefinition/us-core-care-experience-preference,StructureDefinition/us-core-observation-clinical-result,StructureDefinition/us-core-body-temperature,StructureDefinition/us-core-respiratory-rate,StructureDefinition/us-core-observation-screening-assessment,StructureDefinition/pediatric-weight-for-height,StructureDefinition/us-core-observation-pregnancystatus,StructureDefinition/us-core-body-weight,StructureDefinition/us-core-observation-occupation,StructureDefinition/us-core-average-blood-pressure,StructureDefinition/us-core-treatment-intervention-preference,StructureDefinition/us-core-observation-adi-documentation,StructureDefinition/us-core-observation-sexual-orientation,StructureDefinition/us-core-blood-pressure</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -7051,7 +7063,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>StructureDefinition/pediatric-bmi-for-age,StructureDefinition/us-core-pulse-oximetry,StructureDefinition/us-core-observation-pregnancyintent,StructureDefinition/head-occipital-frontal-circumference-percentile,StructureDefinition/us-core-observation-lab,StructureDefinition/us-core-bmi,StructureDefinition/us-core-vital-signs,StructureDefinition/us-core-simple-observation,StructureDefinition/us-core-head-circumference,StructureDefinition/us-core-heart-rate,StructureDefinition/us-core-body-height,StructureDefinition/us-core-smokingstatus,StructureDefinition/us-core-care-experience-preference,StructureDefinition/us-core-observation-clinical-result,StructureDefinition/us-core-observation-screening-assessment,StructureDefinition/us-core-respiratory-rate,StructureDefinition/us-core-body-temperature,StructureDefinition/pediatric-weight-for-height,StructureDefinition/us-core-observation-pregnancystatus,StructureDefinition/us-core-body-weight,StructureDefinition/us-core-observation-occupation,StructureDefinition/us-core-average-blood-pressure,StructureDefinition/us-core-treatment-intervention-preference,StructureDefinition/us-core-observation-adi-documentation,StructureDefinition/us-core-observation-sexual-orientation,StructureDefinition/us-core-blood-pressure</t>
+          <t>StructureDefinition/pediatric-bmi-for-age,StructureDefinition/us-core-pulse-oximetry,StructureDefinition/us-core-observation-pregnancyintent,StructureDefinition/head-occipital-frontal-circumference-percentile,StructureDefinition/us-core-bmi,StructureDefinition/us-core-observation-lab,StructureDefinition/us-core-vital-signs,StructureDefinition/us-core-simple-observation,StructureDefinition/us-core-head-circumference,StructureDefinition/us-core-heart-rate,StructureDefinition/us-core-body-height,StructureDefinition/us-core-smokingstatus,StructureDefinition/us-core-care-experience-preference,StructureDefinition/us-core-observation-clinical-result,StructureDefinition/us-core-body-temperature,StructureDefinition/us-core-respiratory-rate,StructureDefinition/us-core-observation-screening-assessment,StructureDefinition/pediatric-weight-for-height,StructureDefinition/us-core-observation-pregnancystatus,StructureDefinition/us-core-body-weight,StructureDefinition/us-core-observation-occupation,StructureDefinition/us-core-average-blood-pressure,StructureDefinition/us-core-treatment-intervention-preference,StructureDefinition/us-core-observation-adi-documentation,StructureDefinition/us-core-observation-sexual-orientation,StructureDefinition/us-core-blood-pressure</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -7099,7 +7111,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>StructureDefinition/pediatric-bmi-for-age,StructureDefinition/us-core-pulse-oximetry,StructureDefinition/us-core-observation-pregnancyintent,StructureDefinition/head-occipital-frontal-circumference-percentile,StructureDefinition/us-core-observation-lab,StructureDefinition/us-core-bmi,StructureDefinition/us-core-vital-signs,StructureDefinition/us-core-simple-observation,StructureDefinition/us-core-head-circumference,StructureDefinition/us-core-heart-rate,StructureDefinition/us-core-body-height,StructureDefinition/us-core-care-experience-preference,StructureDefinition/us-core-observation-clinical-result,StructureDefinition/us-core-observation-screening-assessment,StructureDefinition/us-core-respiratory-rate,StructureDefinition/us-core-body-temperature,StructureDefinition/pediatric-weight-for-height,StructureDefinition/us-core-observation-pregnancystatus,StructureDefinition/us-core-body-weight,StructureDefinition/us-core-observation-occupation,StructureDefinition/us-core-average-blood-pressure,StructureDefinition/us-core-treatment-intervention-preference,StructureDefinition/us-core-observation-adi-documentation,StructureDefinition/us-core-observation-sexual-orientation,StructureDefinition/us-core-blood-pressure</t>
+          <t>StructureDefinition/pediatric-bmi-for-age,StructureDefinition/us-core-pulse-oximetry,StructureDefinition/us-core-observation-pregnancyintent,StructureDefinition/head-occipital-frontal-circumference-percentile,StructureDefinition/us-core-bmi,StructureDefinition/us-core-observation-lab,StructureDefinition/us-core-vital-signs,StructureDefinition/us-core-simple-observation,StructureDefinition/us-core-head-circumference,StructureDefinition/us-core-heart-rate,StructureDefinition/us-core-body-height,StructureDefinition/us-core-care-experience-preference,StructureDefinition/us-core-observation-clinical-result,StructureDefinition/us-core-body-temperature,StructureDefinition/us-core-respiratory-rate,StructureDefinition/us-core-observation-screening-assessment,StructureDefinition/pediatric-weight-for-height,StructureDefinition/us-core-observation-pregnancystatus,StructureDefinition/us-core-body-weight,StructureDefinition/us-core-observation-occupation,StructureDefinition/us-core-average-blood-pressure,StructureDefinition/us-core-treatment-intervention-preference,StructureDefinition/us-core-observation-adi-documentation,StructureDefinition/us-core-observation-sexual-orientation,StructureDefinition/us-core-blood-pressure</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -7675,7 +7687,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>StructureDefinition/pediatric-bmi-for-age,StructureDefinition/us-core-pulse-oximetry,StructureDefinition/us-core-bmi,StructureDefinition/head-occipital-frontal-circumference-percentile,StructureDefinition/us-core-body-temperature,StructureDefinition/us-core-respiratory-rate,StructureDefinition/pediatric-weight-for-height,StructureDefinition/us-core-head-circumference,StructureDefinition/us-core-heart-rate,StructureDefinition/us-core-body-weight,StructureDefinition/us-core-average-blood-pressure,StructureDefinition/us-core-body-height,StructureDefinition/us-core-blood-pressure</t>
+          <t>StructureDefinition/pediatric-bmi-for-age,StructureDefinition/us-core-pulse-oximetry,StructureDefinition/head-occipital-frontal-circumference-percentile,StructureDefinition/us-core-bmi,StructureDefinition/us-core-body-temperature,StructureDefinition/us-core-respiratory-rate,StructureDefinition/us-core-heart-rate,StructureDefinition/us-core-head-circumference,StructureDefinition/pediatric-weight-for-height,StructureDefinition/us-core-body-weight,StructureDefinition/us-core-average-blood-pressure,StructureDefinition/us-core-body-height,StructureDefinition/us-core-blood-pressure</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -7867,7 +7879,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>StructureDefinition/pediatric-bmi-for-age,StructureDefinition/us-core-pulse-oximetry,StructureDefinition/us-core-observation-pregnancyintent,StructureDefinition/head-occipital-frontal-circumference-percentile,StructureDefinition/us-core-observation-lab,StructureDefinition/us-core-bmi,StructureDefinition/us-core-vital-signs,StructureDefinition/us-core-simple-observation,StructureDefinition/us-core-head-circumference,StructureDefinition/us-core-heart-rate,StructureDefinition/us-core-body-height,StructureDefinition/us-core-smokingstatus,StructureDefinition/us-core-care-experience-preference,StructureDefinition/us-core-observation-clinical-result,StructureDefinition/us-core-observation-screening-assessment,StructureDefinition/us-core-respiratory-rate,StructureDefinition/us-core-body-temperature,StructureDefinition/pediatric-weight-for-height,StructureDefinition/us-core-observation-pregnancystatus,StructureDefinition/us-core-body-weight,StructureDefinition/us-core-observation-occupation,StructureDefinition/us-core-average-blood-pressure,StructureDefinition/us-core-treatment-intervention-preference,StructureDefinition/us-core-observation-adi-documentation,StructureDefinition/us-core-observation-sexual-orientation,StructureDefinition/us-core-blood-pressure</t>
+          <t>StructureDefinition/pediatric-bmi-for-age,StructureDefinition/us-core-pulse-oximetry,StructureDefinition/us-core-observation-pregnancyintent,StructureDefinition/head-occipital-frontal-circumference-percentile,StructureDefinition/us-core-bmi,StructureDefinition/us-core-observation-lab,StructureDefinition/us-core-vital-signs,StructureDefinition/us-core-simple-observation,StructureDefinition/us-core-head-circumference,StructureDefinition/us-core-heart-rate,StructureDefinition/us-core-body-height,StructureDefinition/us-core-smokingstatus,StructureDefinition/us-core-care-experience-preference,StructureDefinition/us-core-observation-clinical-result,StructureDefinition/us-core-body-temperature,StructureDefinition/us-core-respiratory-rate,StructureDefinition/us-core-observation-screening-assessment,StructureDefinition/pediatric-weight-for-height,StructureDefinition/us-core-observation-pregnancystatus,StructureDefinition/us-core-body-weight,StructureDefinition/us-core-observation-occupation,StructureDefinition/us-core-average-blood-pressure,StructureDefinition/us-core-treatment-intervention-preference,StructureDefinition/us-core-observation-adi-documentation,StructureDefinition/us-core-observation-sexual-orientation,StructureDefinition/us-core-blood-pressure</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -7915,7 +7927,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>StructureDefinition/pediatric-bmi-for-age,StructureDefinition/us-core-pulse-oximetry,StructureDefinition/us-core-observation-pregnancyintent,StructureDefinition/head-occipital-frontal-circumference-percentile,StructureDefinition/us-core-observation-lab,StructureDefinition/us-core-bmi,StructureDefinition/us-core-vital-signs,StructureDefinition/us-core-simple-observation,StructureDefinition/us-core-head-circumference,StructureDefinition/us-core-heart-rate,StructureDefinition/us-core-body-height,StructureDefinition/us-core-smokingstatus,StructureDefinition/us-core-care-experience-preference,StructureDefinition/us-core-observation-clinical-result,StructureDefinition/us-core-observation-screening-assessment,StructureDefinition/us-core-respiratory-rate,StructureDefinition/us-core-body-temperature,StructureDefinition/pediatric-weight-for-height,StructureDefinition/us-core-observation-pregnancystatus,StructureDefinition/us-core-body-weight,StructureDefinition/us-core-observation-occupation,StructureDefinition/us-core-average-blood-pressure,StructureDefinition/us-core-treatment-intervention-preference,StructureDefinition/us-core-observation-adi-documentation,StructureDefinition/us-core-observation-sexual-orientation,StructureDefinition/us-core-blood-pressure</t>
+          <t>StructureDefinition/pediatric-bmi-for-age,StructureDefinition/us-core-pulse-oximetry,StructureDefinition/us-core-observation-pregnancyintent,StructureDefinition/head-occipital-frontal-circumference-percentile,StructureDefinition/us-core-bmi,StructureDefinition/us-core-observation-lab,StructureDefinition/us-core-vital-signs,StructureDefinition/us-core-simple-observation,StructureDefinition/us-core-head-circumference,StructureDefinition/us-core-heart-rate,StructureDefinition/us-core-body-height,StructureDefinition/us-core-smokingstatus,StructureDefinition/us-core-care-experience-preference,StructureDefinition/us-core-observation-clinical-result,StructureDefinition/us-core-body-temperature,StructureDefinition/us-core-respiratory-rate,StructureDefinition/us-core-observation-screening-assessment,StructureDefinition/pediatric-weight-for-height,StructureDefinition/us-core-observation-pregnancystatus,StructureDefinition/us-core-body-weight,StructureDefinition/us-core-observation-occupation,StructureDefinition/us-core-average-blood-pressure,StructureDefinition/us-core-treatment-intervention-preference,StructureDefinition/us-core-observation-adi-documentation,StructureDefinition/us-core-observation-sexual-orientation,StructureDefinition/us-core-blood-pressure</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -7928,7 +7940,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/relatedperson-relationshiptype</t>
+          <t>http://hl7.org/fhir/ValueSet/request-intent</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -7943,32 +7955,32 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.3.449</t>
+          <t>2.16.840.1.113883.4.642.3.113</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>PatientRelationshipType</t>
+          <t>RequestIntent</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Patient relationship type</t>
+          <t>RequestIntent</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>A set of codes that can be used to indicate the relationship between a Patient and a Related Person.</t>
+          <t>Codes indicating the degree of authority/intentionality associated with a request.</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-relatedperson</t>
+          <t>StructureDefinition/us-core-servicerequest</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>THO (V3),THO (V2)</t>
+          <t>hl7.fhir.uv.xver-r5.r4</t>
         </is>
       </c>
       <c r="J162" t="inlineStr"/>
@@ -7976,7 +7988,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/request-intent</t>
+          <t>http://hl7.org/fhir/ValueSet/request-priority</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -7991,27 +8003,27 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.3.113</t>
+          <t>2.16.840.1.113883.4.642.3.115</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>RequestIntent</t>
+          <t>RequestPriority</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>RequestIntent</t>
+          <t>Request priority</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Codes indicating the degree of authority/intentionality associated with a request.</t>
+          <t>The clinical priority of a diagnostic order.</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-servicerequest</t>
+          <t>StructureDefinition/us-core-medicationrequest,StructureDefinition/us-core-servicerequest</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -8024,7 +8036,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/request-priority</t>
+          <t>http://hl7.org/fhir/ValueSet/request-status</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -8039,27 +8051,27 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.3.115</t>
+          <t>2.16.840.1.113883.4.642.3.111</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>RequestPriority</t>
+          <t>RequestStatus</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Request priority</t>
+          <t>RequestStatus</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>The clinical priority of a diagnostic order.</t>
+          <t>Codes identifying the lifecycle stage of a request.</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-medicationrequest,StructureDefinition/us-core-servicerequest</t>
+          <t>StructureDefinition/us-core-careplan,StructureDefinition/us-core-servicerequest</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -8072,7 +8084,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/request-status</t>
+          <t>http://hl7.org/fhir/ValueSet/resource-types</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -8082,37 +8094,37 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>active</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.3.111</t>
+          <t>2.16.840.1.113883.4.642.3.27</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>RequestStatus</t>
+          <t>ResourceType</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>RequestStatus</t>
+          <t>ResourceType</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Codes identifying the lifecycle stage of a request.</t>
+          <t>One of the resource types defined as part of this version of FHIR.</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-careplan,StructureDefinition/us-core-servicerequest</t>
+          <t>StructureDefinition/us-core-provenance,StructureDefinition/us-core-questionnaireresponse</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>hl7.fhir.uv.xver-r5.r4</t>
+          <t>hl7.fhir.r4.core</t>
         </is>
       </c>
       <c r="J165" t="inlineStr"/>
@@ -8120,7 +8132,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+          <t>http://hl7.org/fhir/ValueSet/route-codes</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -8130,37 +8142,37 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.3.27</t>
+          <t>2.16.840.1.113883.4.642.3.98</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>ResourceType</t>
+          <t>SNOMEDCTRouteCodes</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>ResourceType</t>
+          <t>SNOMED CT Route Codes</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>One of the resource types defined as part of this version of FHIR.</t>
+          <t>This value set includes all Route codes from SNOMED CT - provided as an exemplar.</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-provenance</t>
+          <t>StructureDefinition/us-core-allergyintolerance</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>hl7.fhir.r4.core</t>
+          <t>SCT</t>
         </is>
       </c>
       <c r="J166" t="inlineStr"/>
@@ -8168,7 +8180,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/route-codes</t>
+          <t>http://hl7.org/fhir/ValueSet/security-labels</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -8178,45 +8190,41 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>active</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.3.98</t>
+          <t>2.16.840.1.113883.4.642.3.47</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>SNOMEDCTRouteCodes</t>
+          <t>All Security Labels</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>SNOMED CT Route Codes</t>
+          <t>SecurityLabels</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>This value set includes all Route codes from SNOMED CT - provided as an exemplar.</t>
+          <t>A single value set for all security labels defined by FHIR.</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-allergyintolerance</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>SCT</t>
-        </is>
-      </c>
+          <t>StructureDefinition/us-core-adi-documentreference,StructureDefinition/us-core-condition-problems-health-concerns,StructureDefinition/us-core-diagnosticreport-lab,StructureDefinition/us-core-documentreference,StructureDefinition/us-core-encounter,StructureDefinition/us-core-observation-lab</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+          <t>http://hl7.org/fhir/ValueSet/security-role-type</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -8226,41 +8234,45 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.3.47</t>
+          <t>2.16.840.1.113883.4.642.3.978</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>All Security Labels</t>
+          <t>SecurityRoleType</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>SecurityLabels</t>
+          <t>SecurityRoleType</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>A single value set for all security labels defined by FHIR.</t>
+          <t>This example FHIR value set is comprised of example Actor Type codes, which can be used to value FHIR agents, actors, and other role         elements such as those specified in financial transactions. The FHIR Actor value set is based on    DICOM Audit Message, C402;   ASTM Standard, E1762-95 [2013]; selected codes and          derived actor roles from HL7 RoleClass OID 2.16.840.1.113883.5.110;    HL7 Role Code 2.16.840.1.113883.5.111, including AgentRoleType;          HL7 ParticipationType OID: 2.16.840.1.113883.5.90; and    HL7 ParticipationFunction codes OID: 2.16.840.1.113883.5.88.           This value set includes, by reference, role codes from external code systems: NUCC Health Care Provider Taxonomy OID: 2.16.840.1.113883.6.101;          North American Industry Classification System [NAICS]OID: 2.16.840.1.113883.6.85; IndustryClassificationSystem 2.16.840.1.113883.1.11.16039;          and US Census Occupation Code OID: 2.16.840.1.113883.6.243 for relevant recipient or custodian codes not included in this value set.            If no source is indicated in the definition comments, then these are example FHIR codes.          It can be extended with appropriate roles described by SNOMED as well as those described in the HL7 Role Based Access Control Catalog and the          HL7 Healthcare (Security and Privacy) Access Control Catalog.            In Role-Based Access Control (RBAC), permissions are operations on an object that a user wishes to access. Permissions are grouped into roles.          A role characterizes the functions a user is allowed to perform. Roles are assigned to users. If the user's role has the appropriate permissions          to access an object, then that user is granted access to the object. FHIR readily enables RBAC, as FHIR Resources are object types and the CRUDE          events (the FHIR equivalent to permissions in the RBAC scheme) are operations on those objects.          In Attribute-Based Access Control (ABAC), a user requests to perform operations on objects. That user's access request is granted or denied          based on a set of access control policies that are specified in terms of attributes and conditions. FHIR readily enables ABAC, as instances of          a Resource in FHIR (again, Resources are object types) can have attributes associated with them. These attributes include security tags,          environment conditions, and a host of user and object characteristics, which are the same attributes as those used in ABAC. Attributes help          define the access control policies that determine the operations a user may perform on a Resource (in FHIR) or object (in ABAC). For example,          a tag (or attribute) may specify that the identified Resource (object) is not to be further disclosed without explicit consent from the patient.</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-adi-documentreference,StructureDefinition/us-core-condition-problems-health-concerns,StructureDefinition/us-core-diagnosticreport-lab,StructureDefinition/us-core-documentreference,StructureDefinition/us-core-encounter,StructureDefinition/us-core-observation-lab</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr"/>
+          <t>StructureDefinition/us-core-provenance</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>THO (V3),THO,DICOM</t>
+        </is>
+      </c>
       <c r="J168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/security-role-type</t>
+          <t>http://hl7.org/fhir/ValueSet/service-type</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -8275,32 +8287,32 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.3.978</t>
+          <t>2.16.840.1.113883.4.642.3.518</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>SecurityRoleType</t>
+          <t>ServiceType</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>SecurityRoleType</t>
+          <t>Service type</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>This example FHIR value set is comprised of example Actor Type codes, which can be used to value FHIR agents, actors, and other role         elements such as those specified in financial transactions. The FHIR Actor value set is based on    DICOM Audit Message, C402;   ASTM Standard, E1762-95 [2013]; selected codes and          derived actor roles from HL7 RoleClass OID 2.16.840.1.113883.5.110;    HL7 Role Code 2.16.840.1.113883.5.111, including AgentRoleType;          HL7 ParticipationType OID: 2.16.840.1.113883.5.90; and    HL7 ParticipationFunction codes OID: 2.16.840.1.113883.5.88.           This value set includes, by reference, role codes from external code systems: NUCC Health Care Provider Taxonomy OID: 2.16.840.1.113883.6.101;          North American Industry Classification System [NAICS]OID: 2.16.840.1.113883.6.85; IndustryClassificationSystem 2.16.840.1.113883.1.11.16039;          and US Census Occupation Code OID: 2.16.840.1.113883.6.243 for relevant recipient or custodian codes not included in this value set.            If no source is indicated in the definition comments, then these are example FHIR codes.          It can be extended with appropriate roles described by SNOMED as well as those described in the HL7 Role Based Access Control Catalog and the          HL7 Healthcare (Security and Privacy) Access Control Catalog.            In Role-Based Access Control (RBAC), permissions are operations on an object that a user wishes to access. Permissions are grouped into roles.          A role characterizes the functions a user is allowed to perform. Roles are assigned to users. If the user's role has the appropriate permissions          to access an object, then that user is granted access to the object. FHIR readily enables RBAC, as FHIR Resources are object types and the CRUDE          events (the FHIR equivalent to permissions in the RBAC scheme) are operations on those objects.          In Attribute-Based Access Control (ABAC), a user requests to perform operations on objects. That user's access request is granted or denied          based on a set of access control policies that are specified in terms of attributes and conditions. FHIR readily enables ABAC, as instances of          a Resource in FHIR (again, Resources are object types) can have attributes associated with them. These attributes include security tags,          environment conditions, and a host of user and object characteristics, which are the same attributes as those used in ABAC. Attributes help          define the access control policies that determine the operations a user may perform on a Resource (in FHIR) or object (in ABAC). For example,          a tag (or attribute) may specify that the identified Resource (object) is not to be further disclosed without explicit consent from the patient.</t>
+          <t>This value set defines an example set of codes of service-types.</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-provenance</t>
+          <t>StructureDefinition/us-core-encounter</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>THO (V3),THO,DICOM</t>
+          <t>THO</t>
         </is>
       </c>
       <c r="J169" t="inlineStr"/>
@@ -8308,7 +8320,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/service-type</t>
+          <t>http://hl7.org/fhir/ValueSet/servicerequest-category</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -8323,32 +8335,32 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.3.518</t>
+          <t>2.16.840.1.113883.4.642.3.434</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>ServiceType</t>
+          <t>ServiceRequestCategoryCodes</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Service type</t>
+          <t>Service Request Category Codes</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>This value set defines an example set of codes of service-types.</t>
+          <t>An example value set of SNOMED CT concepts that can classify a requested service</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-encounter</t>
+          <t>ValueSet/us-core-servicerequest-category,StructureDefinition/us-core-servicerequest</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>THO</t>
+          <t>SCT</t>
         </is>
       </c>
       <c r="J170" t="inlineStr"/>
@@ -8356,7 +8368,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/servicerequest-category</t>
+          <t>http://hl7.org/fhir/ValueSet/servicerequest-orderdetail</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -8371,27 +8383,27 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.3.434</t>
+          <t>2.16.840.1.113883.4.642.3.435</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>ServiceRequestCategoryCodes</t>
+          <t>ServiceRequestOrderDetailsCodes</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Service Request Category Codes</t>
+          <t>Service Request Order Details Codes</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>An example value set of SNOMED CT concepts that can classify a requested service</t>
+          <t>An example value set of Codified order entry details concepts.  These concepts only make sense in the context of what is being ordered.  This example is for a patient ventilation order</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>ValueSet/us-core-servicerequest-category,StructureDefinition/us-core-servicerequest</t>
+          <t>StructureDefinition/us-core-servicerequest</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -8404,7 +8416,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/servicerequest-orderdetail</t>
+          <t>http://hl7.org/fhir/ValueSet/specimen-collection-method</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -8419,27 +8431,27 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.3.435</t>
+          <t>2.16.840.1.113883.4.642.3.468</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>ServiceRequestOrderDetailsCodes</t>
+          <t>FHIRSpecimenCollectionMethod</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Service Request Order Details Codes</t>
+          <t>FHIR Specimen Collection Method</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>An example value set of Codified order entry details concepts.  These concepts only make sense in the context of what is being ordered.  This example is for a patient ventilation order</t>
+          <t xml:space="preserve"> This example value set defines a set of codes that can be used to indicate the method by which a specimen was collected.</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-servicerequest</t>
+          <t>StructureDefinition/us-core-specimen</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -8452,7 +8464,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/specimen-collection-method</t>
+          <t>http://hl7.org/fhir/ValueSet/specimen-container-type</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -8467,22 +8479,22 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.3.468</t>
+          <t>2.16.840.1.113883.4.642.3.470</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>FHIRSpecimenCollectionMethod</t>
+          <t>SpecimenContainerType</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>FHIR Specimen Collection Method</t>
+          <t>Specimen Container Type</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve"> This example value set defines a set of codes that can be used to indicate the method by which a specimen was collected.</t>
+          <t>Checks on the patient prior specimen collection. All SNOMED CT concepts descendants of 706041008 |Device for body fluid and tissue collection/transfer/processing (physical object)|</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -8500,7 +8512,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/specimen-container-type</t>
+          <t>http://hl7.org/fhir/ValueSet/specimen-processing-procedure</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -8515,22 +8527,22 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.3.470</t>
+          <t>2.16.840.1.113883.4.642.3.469</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>SpecimenContainerType</t>
+          <t>SpecimenProcessingProcedure</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Specimen Container Type</t>
+          <t>Specimen processing procedure</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Checks on the patient prior specimen collection. All SNOMED CT concepts descendants of 706041008 |Device for body fluid and tissue collection/transfer/processing (physical object)|</t>
+          <t>The technique that is used to perform the process or preserve the specimen.</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -8540,7 +8552,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>SCT</t>
+          <t>THO (V2)</t>
         </is>
       </c>
       <c r="J174" t="inlineStr"/>
@@ -8548,7 +8560,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/specimen-processing-procedure</t>
+          <t>http://hl7.org/fhir/ValueSet/specimen-status</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -8563,22 +8575,22 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.3.469</t>
+          <t>2.16.840.1.113883.4.642.3.471</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>SpecimenProcessingProcedure</t>
+          <t>SpecimenStatus</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Specimen processing procedure</t>
+          <t>SpecimenStatus</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>The technique that is used to perform the process or preserve the specimen.</t>
+          <t>Codes providing the status/availability of a specimen.</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -8588,7 +8600,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>THO (V2)</t>
+          <t>hl7.fhir.uv.xver-r5.r4</t>
         </is>
       </c>
       <c r="J175" t="inlineStr"/>
@@ -8596,7 +8608,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/specimen-status</t>
+          <t>http://hl7.org/fhir/ValueSet/subscriber-relationship</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -8611,32 +8623,32 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.3.471</t>
+          <t>2.16.840.1.113883.4.642.3.1385</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>SpecimenStatus</t>
+          <t>SubscriberRelationshipCodes</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>SpecimenStatus</t>
+          <t>SubscriberPolicyholder Relationship Codes</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Codes providing the status/availability of a specimen.</t>
+          <t>This value set includes codes for the relationship between the Subscriber and the Beneficiary (insured/covered party/patient).</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-specimen</t>
+          <t>StructureDefinition/us-core-coverage</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>hl7.fhir.uv.xver-r5.r4</t>
+          <t>THO</t>
         </is>
       </c>
       <c r="J176" t="inlineStr"/>
@@ -8644,7 +8656,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/subscriber-relationship</t>
+          <t>http://hl7.org/fhir/ValueSet/substance-code</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -8659,32 +8671,32 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.3.1385</t>
+          <t>2.16.840.1.113883.4.642.3.473</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>SubscriberRelationshipCodes</t>
+          <t>SubstanceCode</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>SubscriberPolicyholder Relationship Codes</t>
+          <t>Substance Code</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>This value set includes codes for the relationship between the Subscriber and the Beneficiary (insured/covered party/patient).</t>
+          <t>This value set contains concept codes for specific substances. It includes codes from [SNOMED](http://snomed.info/sct) where concept is-a 105590001 (Substance (substance)) and where concept is-a 373873005 (Pharmaceutical / biologic product (product))</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-coverage</t>
+          <t>StructureDefinition/us-core-allergyintolerance</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>THO</t>
+          <t>SCT</t>
         </is>
       </c>
       <c r="J177" t="inlineStr"/>
@@ -8692,7 +8704,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/substance-code</t>
+          <t>http://hl7.org/fhir/ValueSet/ucum-bodylength</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -8707,32 +8719,32 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.3.473</t>
+          <t>2.16.840.1.113883.4.642.3.958</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>SubstanceCode</t>
+          <t>BodyLengthUnits</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Substance Code</t>
+          <t>Body Length Units</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>This value set contains concept codes for specific substances. It includes codes from [SNOMED](http://snomed.info/sct) where concept is-a 105590001 (Substance (substance)) and where concept is-a 373873005 (Pharmaceutical / biologic product (product))</t>
+          <t>UCUM units for recording body length measures such as height and head circumference</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-allergyintolerance</t>
+          <t>StructureDefinition/us-core-head-circumference,StructureDefinition/us-core-body-height</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>SCT</t>
+          <t>UCUM</t>
         </is>
       </c>
       <c r="J178" t="inlineStr"/>
@@ -8740,7 +8752,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/ucum-bodylength</t>
+          <t>http://hl7.org/fhir/ValueSet/ucum-bodytemp</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -8755,27 +8767,27 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.3.958</t>
+          <t>2.16.840.1.113883.4.642.3.957</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>BodyLengthUnits</t>
+          <t>BodyTemperatureUnits</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Body Length Units</t>
+          <t>Body Temperature Units</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>UCUM units for recording body length measures such as height and head circumference</t>
+          <t>UCUM units for recording Body Temperature</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-head-circumference,StructureDefinition/us-core-body-height</t>
+          <t>StructureDefinition/us-core-body-temperature</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -8788,7 +8800,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/ucum-bodytemp</t>
+          <t>http://hl7.org/fhir/ValueSet/ucum-bodyweight</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -8803,27 +8815,27 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.3.957</t>
+          <t>2.16.840.1.113883.4.642.3.956</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>BodyTemperatureUnits</t>
+          <t>BodyWeightUnits</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Body Temperature Units</t>
+          <t>Body Weight Units</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>UCUM units for recording Body Temperature</t>
+          <t>UCUM units for recording Body Weight</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-body-temperature</t>
+          <t>StructureDefinition/us-core-body-weight</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -8836,7 +8848,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/ucum-bodyweight</t>
+          <t>http://hl7.org/fhir/ValueSet/ucum-common</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -8849,29 +8861,21 @@
           <t>draft</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>2.16.840.1.113883.4.642.3.956</t>
-        </is>
-      </c>
+      <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
-          <t>BodyWeightUnits</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>Body Weight Units</t>
-        </is>
-      </c>
+          <t>Common UCUM units</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr">
         <is>
-          <t>UCUM units for recording Body Weight</t>
+          <t>Commonly encountered UCUM units (for purposes of helping populate look ups.</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-body-weight</t>
+          <t>StructureDefinition/us-core-medicationrequest,StructureDefinition/us-core-medicationdispense</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -8884,7 +8888,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/ucum-common</t>
+          <t>http://hl7.org/fhir/ValueSet/ucum-vitals-common</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -8897,21 +8901,29 @@
           <t>draft</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>2.16.840.1.113883.4.642.3.955</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Common UCUM units</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr"/>
+          <t>VitalSignsUnits</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Vital Signs Units</t>
+        </is>
+      </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Commonly encountered UCUM units (for purposes of helping populate look ups.</t>
+          <t>Common UCUM units for recording Vital Signs</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-medicationrequest,StructureDefinition/us-core-medicationdispense</t>
+          <t>StructureDefinition/pediatric-bmi-for-age,StructureDefinition/us-core-pulse-oximetry,StructureDefinition/head-occipital-frontal-circumference-percentile,StructureDefinition/us-core-bmi,StructureDefinition/us-core-body-temperature,StructureDefinition/us-core-respiratory-rate,StructureDefinition/us-core-vital-signs,StructureDefinition/us-core-heart-rate,StructureDefinition/us-core-head-circumference,StructureDefinition/pediatric-weight-for-height,StructureDefinition/us-core-body-weight,StructureDefinition/us-core-body-height,StructureDefinition/us-core-blood-pressure</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -8924,7 +8936,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/ucum-vitals-common</t>
+          <t>http://hl7.org/fhir/ValueSet/udi-entry-type</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -8939,32 +8951,32 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.3.955</t>
+          <t>2.16.840.1.113883.4.642.3.211</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>VitalSignsUnits</t>
+          <t>UDIEntryType</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Vital Signs Units</t>
+          <t>UDIEntryType</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Common UCUM units for recording Vital Signs</t>
+          <t>Codes to identify how UDI data was entered.</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>StructureDefinition/pediatric-bmi-for-age,StructureDefinition/us-core-pulse-oximetry,StructureDefinition/us-core-bmi,StructureDefinition/head-occipital-frontal-circumference-percentile,StructureDefinition/us-core-body-temperature,StructureDefinition/us-core-respiratory-rate,StructureDefinition/us-core-vital-signs,StructureDefinition/pediatric-weight-for-height,StructureDefinition/us-core-head-circumference,StructureDefinition/us-core-heart-rate,StructureDefinition/us-core-body-weight,StructureDefinition/us-core-body-height,StructureDefinition/us-core-blood-pressure</t>
+          <t>StructureDefinition/us-core-device</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>UCUM</t>
+          <t>hl7.fhir.uv.xver-r5.r4</t>
         </is>
       </c>
       <c r="J183" t="inlineStr"/>
@@ -8972,47 +8984,47 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/ValueSet/udi-entry-type</t>
+          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-clinical-note-type</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>4.0.1</t>
+          <t>9.0.0</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>active</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.3.211</t>
+          <t>2.16.840.1.113883.4.642.40.2.48.1</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>UDIEntryType</t>
+          <t>USCoreClinicalNoteType</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>UDIEntryType</t>
+          <t>US Core Clinical Note Type</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Codes to identify how UDI data was entered.</t>
+          <t>The US Core Clinical Note Type Value Set is a 'starter set' of types supported for fetching and storing clinical notes.</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-device</t>
+          <t>StructureDefinition/us-core-documentreference</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>hl7.fhir.uv.xver-r5.r4</t>
+          <t>LOINC</t>
         </is>
       </c>
       <c r="J184" t="inlineStr"/>
@@ -9020,7 +9032,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-clinical-note-type</t>
+          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-clinical-result-observation-category</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -9035,28 +9047,32 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.40.2.48.1</t>
+          <t>2.16.840.1.113883.4.642.40.2.48.2</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>USCoreClinicalNoteType</t>
+          <t>USCoreClinicalResultObservationCategory</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>US Core Clinical Note Type</t>
+          <t>US Core Clinical Result Observation Category</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>The US Core Clinical Note Type Value Set is a 'starter set' of types supported for fetching and storing clinical notes.</t>
-        </is>
-      </c>
-      <c r="H185" t="inlineStr"/>
+          <t>Used to classify the context of clinical result observations.</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>StructureDefinition/us-core-observation-clinical-result,StructureDefinition/us-core-observation-lab</t>
+        </is>
+      </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>LOINC</t>
+          <t>THO</t>
         </is>
       </c>
       <c r="J185" t="inlineStr"/>
@@ -9064,7 +9080,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-clinical-result-observation-category</t>
+          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-condition-code</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -9079,32 +9095,32 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.40.2.48.2</t>
+          <t>2.16.840.1.113883.4.642.40.2.48.16</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>USCoreClinicalResultObservationCategory</t>
+          <t>USCoreConditionCodes</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>US Core Clinical Result Observation Category</t>
+          <t>US Core Condition Codes</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Used to classify the context of clinical result observations.</t>
+          <t>This describes the problem. Diagnosis/Problem List is broadly defined as a series of brief statements that catalog a patient's medical, nursing, dental, social, preventative and psychiatric events and issues that are relevant to that patient's healthcare (e.g., signs, symptoms, and defined conditions). ICD-10 is appropriate for Diagnosis information, and ICD-9 for historical information.</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-observation-lab,StructureDefinition/us-core-observation-clinical-result</t>
+          <t>StructureDefinition/us-core-condition-problems-health-concerns,StructureDefinition/us-core-medicationrequest,StructureDefinition/us-core-procedure,StructureDefinition/us-core-servicerequest,StructureDefinition/us-core-familymemberhistory,StructureDefinition/us-core-condition-encounter-diagnosis</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>THO</t>
+          <t>SCT,hl7.terminology.r4</t>
         </is>
       </c>
       <c r="J186" t="inlineStr"/>
@@ -9112,7 +9128,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-condition-code</t>
+          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-diagnosticreport-category</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -9127,32 +9143,32 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.40.2.48.15</t>
+          <t>2.16.840.1.113883.4.642.40.2.48.3</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>USCoreConditionCodes</t>
+          <t>USCoreDiagnosticReportCategory</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>US Core Condition Codes</t>
+          <t>US Core Diagnostic Report Category Codes</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>This describes the problem. Diagnosis/Problem List is broadly defined as a series of brief statements that catalog a patient's medical, nursing, dental, social, preventative and psychiatric events and issues that are relevant to that patient's healthcare (e.g., signs, symptoms, and defined conditions). ICD-10 is appropriate for Diagnosis information, and ICD-9 for historical information.</t>
+          <t>The US Core Diagnostic Report Category Value Set is a 'starter set' of categories supported for fetching and Diagnostic Reports and notes.</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-condition-problems-health-concerns,StructureDefinition/us-core-medicationrequest,StructureDefinition/us-core-procedure,StructureDefinition/us-core-servicerequest,StructureDefinition/us-core-familymemberhistory,StructureDefinition/us-core-condition-encounter-diagnosis</t>
+          <t>StructureDefinition/us-core-diagnosticreport-note</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>SCT,hl7.terminology.r4</t>
+          <t>LOINC</t>
         </is>
       </c>
       <c r="J187" t="inlineStr"/>
@@ -9160,7 +9176,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-condition-code-current</t>
+          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-diagnosticreport-report-and-note-codes</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -9175,32 +9191,32 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.40.2.48.3</t>
+          <t>2.16.840.1.113883.4.642.40.2.48.4</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>USCoreConditionCodesCurrent</t>
+          <t>USCoreNonLaboratoryCodes</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>US Core Condition Codes Current</t>
+          <t>US Core Non Laboratory Codes</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>This valueset is defined the same as the [US Core Condition Codes](ValueSet-us-core-condition-code.html) value set except it excludes ICD-9-CM codes. It us used for encoding newly recorded, non-legacy problem list items, health concerns and diagnosis using SNOMED CT and ICD-10-CM per USCDI requirements.</t>
+          <t>This value set includes All LOINC codes defined as type "clinical," therefore excluding laboratory tests, survey instruments, and claims documents. This includes observables such as vital signs, hemodynamics, intake/output, EKG, obstetric ultrasound, and cardiac echo, and includes discrete and narrative diagnostic observations and reports.</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-condition-problems-health-concerns,StructureDefinition/us-core-condition-encounter-diagnosis</t>
+          <t>StructureDefinition/us-core-diagnosticreport-note</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>SCT,hl7.terminology.r4</t>
+          <t>LOINC</t>
         </is>
       </c>
       <c r="J188" t="inlineStr"/>
@@ -9208,7 +9224,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-diagnosticreport-category</t>
+          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-documentreference-category</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -9223,32 +9239,32 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.40.2.48.4</t>
+          <t>2.16.840.1.113883.4.642.40.2.48.5</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>USCoreDiagnosticReportCategory</t>
+          <t>USCoreDocumentReferenceCategory</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>US Core Diagnostic Report Category Codes</t>
+          <t>US Core DocumentReference Category</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>The US Core Diagnostic Report Category Value Set is a 'starter set' of categories supported for fetching and Diagnostic Reports and notes.</t>
+          <t>The US Core DocumentReferences Category Value Set is a 'starter set' of categories supported for fetching and storing clinical notes.</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-diagnosticreport-note</t>
+          <t>StructureDefinition/us-core-documentreference</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>LOINC</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="J189" t="inlineStr"/>
@@ -9256,7 +9272,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-diagnosticreport-report-and-note-codes</t>
+          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-documentreference-type</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -9271,32 +9287,32 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.40.2.48.5</t>
+          <t>2.16.840.1.113883.4.642.40.2.48.6</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>USCoreNonLaboratoryCodes</t>
+          <t>USCoreDocumentReferenceType</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>US Core Non Laboratory Codes</t>
+          <t>US Core DocumentReference Type</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>This value set includes All LOINC codes defined as type "clinical," therefore excluding laboratory tests, survey instruments, and claims documents. This includes observables such as vital signs, hemodynamics, intake/output, EKG, obstetric ultrasound, and cardiac echo, and includes discrete and narrative diagnostic observations and reports.</t>
+          <t>The US Core DocumentReference Type Value Set includes all LOINC values whose SCALE is "Doc" in the LOINC database and the HL7 v3 Code System NullFlavor concept 'unknown'</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-diagnosticreport-note</t>
+          <t>StructureDefinition/us-core-documentreference</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>LOINC</t>
+          <t>THO (V3),LOINC</t>
         </is>
       </c>
       <c r="J190" t="inlineStr"/>
@@ -9304,7 +9320,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-documentreference-category</t>
+          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-goal-description</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -9319,32 +9335,32 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.40.2.48.6</t>
+          <t>2.16.840.1.113883.4.642.40.2.48.17</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>USCoreDocumentReferenceCategory</t>
+          <t>USCoreGoalCodes</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>US Core DocumentReference Category</t>
+          <t>US Core Goal Codes</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>The US Core DocumentReferences Category Value Set is a 'starter set' of categories supported for fetching and storing clinical notes.</t>
+          <t>Concepts from SNOMED CT and LOINC code systems that can be used to indicate the goal.</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-documentreference</t>
+          <t>StructureDefinition/us-core-goal</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>SCT,LOINC</t>
         </is>
       </c>
       <c r="J191" t="inlineStr"/>
@@ -9352,7 +9368,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-documentreference-type</t>
+          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-laboratory-test-codes</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -9367,32 +9383,32 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.40.2.48.7</t>
+          <t>2.16.840.1.113883.4.642.40.2.48.18</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>USCoreDocumentReferenceType</t>
+          <t>USCoreLaboratoryTestCodes</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>US Core DocumentReference Type</t>
+          <t>US Core Laboratory Test Codes</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>The US Core DocumentReference Type Value Set includes all LOINC values whose SCALE is "Doc" in the LOINC database and the HL7 v3 Code System NullFlavor concept 'unknown'</t>
+          <t>Laboratory LOINC codes: From the introduction to August 2022 LOINC Users' guide; "The current scope of the existing laboratory portion of the LOINC  database includes all observations reported by clinical laboratories, including the specialty areas: chemistry, including therapeutic drug monitoring and toxicology; hematology; serology; blood bank; microbiology; cytology; surgical pathology; and fertility.</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-documentreference</t>
+          <t>StructureDefinition/us-core-diagnosticreport-lab,StructureDefinition/us-core-observation-lab</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>THO (V3),LOINC</t>
+          <t>LOINC</t>
         </is>
       </c>
       <c r="J192" t="inlineStr"/>
@@ -9400,7 +9416,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-goal-description</t>
+          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-location-type</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -9415,40 +9431,36 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.40.2.48.16</t>
+          <t>2.16.840.1.113883.4.642.40.2.48.7</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>USCoreGoalCodes</t>
+          <t>USCoreLocationType</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>US Core Goal Codes</t>
+          <t>US Core Location Type Codes</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Concepts from SNOMED CT  and LOINC code systems that can be used to indicate the goal.</t>
+          <t>This value set represents the types of locations and organizational settings where healthcare services, encounters, or treatments occur, and is composed of several value sets to meet multiple industry needs. It includes HL7 Terminology (THO), SNOMED CT, National Healthcare Safety Network (NHSN), and CMS Place of Service Codes (POS) concepts.</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-goal</t>
-        </is>
-      </c>
-      <c r="I193" t="inlineStr">
-        <is>
-          <t>SCT,LOINC</t>
-        </is>
-      </c>
+          <t>StructureDefinition/us-core-location</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-laboratory-test-codes</t>
+          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-narrative-status</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -9463,32 +9475,32 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.40.2.48.17</t>
+          <t>2.16.840.1.113883.4.642.40.2.48.8</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>USCoreLaboratoryTestCodes</t>
+          <t>NarrativeStatus</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>US Core Laboratory Test Codes</t>
+          <t>US Core Narrative Status</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Laboratory LOINC codes: From the introduction to August 2022 LOINC Users' guide; "The current scope of the existing laboratory portion of the LOINC  database includes all observations reported by clinical laboratories, including the specialty areas: chemistry, including therapeutic drug monitoring and toxicology; hematology; serology; blood bank; microbiology; cytology; surgical pathology; and fertility.</t>
+          <t>The US Core Narrative Status Value Set limits the text status for the resource narrative.</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-diagnosticreport-lab,StructureDefinition/us-core-observation-lab</t>
+          <t>StructureDefinition/us-core-careplan</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>LOINC</t>
+          <t>hl7.fhir.uv.xver-r5.r4</t>
         </is>
       </c>
       <c r="J194" t="inlineStr"/>
@@ -9496,7 +9508,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-narrative-status</t>
+          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-observation-smoking-status-status</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -9511,27 +9523,27 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.40.2.48.8</t>
+          <t>2.16.840.1.113883.4.642.40.2.48.9</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>NarrativeStatus</t>
+          <t>USCoreObservationSmokingStatusStatus</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>US Core Narrative Status</t>
+          <t>US Core Status for Smoking Status Observation</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>The US Core Narrative Status Value Set limits the text status for the resource narrative.</t>
+          <t>Codes providing the status of an observation for smoking status. Constrained to `final` and `entered-in-error`.</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-careplan</t>
+          <t>StructureDefinition/us-core-smokingstatus</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -9544,7 +9556,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-observation-smoking-status-status</t>
+          <t>http://hl7.org/fhir/us/core/ValueSet/us-core-practitionerrole-specialty</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -9559,34 +9571,30 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.40.2.48.9</t>
+          <t>2.16.840.1.113883.4.642.40.2.48.10</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>USCoreObservationSmokingStatusStatus</t>
+          <t>USCorePractitionerRoleSpecialty</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>US Core Status for Smoking Status Observation</t>
+          <t>US Core Practitioner Role Specialty Codes</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Codes providing the status of an observation for smoking status. Constrained to `final`and `entered-in-error`.</t>
+          <t>This value set represents the clinical specialty or functional role played by a clinician or provider. It is composed of two value sets, and include the National Uniform Claims Committee (NUCC) and SNOMED CT concepts.</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-smokingstatus</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>hl7.fhir.uv.xver-r5.r4</t>
-        </is>
-      </c>
+          <t>StructureDefinition/us-core-practitionerrole</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr"/>
       <c r="J196" t="inlineStr"/>
     </row>
     <row r="197">
@@ -9607,7 +9615,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.40.2.48.18</t>
+          <t>2.16.840.1.113883.4.642.40.2.48.19</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -9655,7 +9663,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.40.2.48.19</t>
+          <t>2.16.840.1.113883.4.642.40.2.48.20</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -9670,7 +9678,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Concepts from CPT, SNOMED CT, HCPCS Level II Alphanumeric Codes, ICD-10-PCS,CDT and LOINC code systems that can be used to indicate the type of procedure performed.</t>
+          <t>Concepts from CPT, SNOMED CT, HCPCS Level II Alphanumeric Codes, ICD-10-PCS, CDT and LOINC code systems that can be used to indicate the type of procedure performed.</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -9703,7 +9711,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.40.2.48.10</t>
+          <t>2.16.840.1.113883.4.642.40.2.48.11</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -9721,7 +9729,11 @@
           <t>This value set consists of the single code "sdoh". It is the minimum value set of category codes used in the US Core Condition Problems and Health Concerns Profile that any conformant system **SHALL** support to help identify the type of USCDI Health Status/Assessment data class being reported.</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr"/>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>StructureDefinition/us-core-condition-problems-health-concerns</t>
+        </is>
+      </c>
       <c r="I199" t="inlineStr">
         <is>
           <t>Internal</t>
@@ -9747,7 +9759,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.40.2.48.11</t>
+          <t>2.16.840.1.113883.4.642.40.2.48.12</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -9767,7 +9779,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-condition-problems-health-concerns,StructureDefinition/us-core-observation-screening-assessment</t>
+          <t>StructureDefinition/us-core-observation-screening-assessment</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -9795,7 +9807,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.40.2.48.12</t>
+          <t>2.16.840.1.113883.4.642.40.2.48.13</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -9843,7 +9855,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.40.2.48.20</t>
+          <t>2.16.840.1.113883.4.642.40.2.48.21</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -9891,7 +9903,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.40.2.48.13</t>
+          <t>2.16.840.1.113883.4.642.40.2.48.14</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -9939,7 +9951,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.4.642.40.2.48.14</t>
+          <t>2.16.840.1.113883.4.642.40.2.48.15</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -10083,7 +10095,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-location</t>
+          <t>ValueSet/us-core-location-type</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -10237,7 +10249,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2.0.0</t>
+          <t>3.0.0</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -10285,7 +10297,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2.0.0</t>
+          <t>3.0.0</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -10333,7 +10345,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2.0.0</t>
+          <t>3.0.0</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -10381,7 +10393,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2.0.0</t>
+          <t>3.0.0</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -10429,7 +10441,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2.0.0</t>
+          <t>3.0.0</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -10887,7 +10899,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>StructureDefinition/us-core-location,StructureDefinition/us-core-servicerequest</t>
+          <t>ValueSet/us-core-location-type,StructureDefinition/us-core-servicerequest</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
